--- a/figs/exps/performance_parsed.xlsx
+++ b/figs/exps/performance_parsed.xlsx
@@ -441,47 +441,47 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Frame</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>结果</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>逻辑链Acc</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>相关性Acc</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>总Acc</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Level 1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Level 2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Level 3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 8</t>
         </is>
       </c>
     </row>
@@ -519,27 +519,29 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>64</v>
+      </c>
+      <c r="D3" t="n">
         <v>11</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>29.6</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>25.1</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>26.6</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>15.84564860426929</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>9.783333333333333</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>9.118773946360154</v>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -559,27 +561,29 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>64</v>
+      </c>
+      <c r="D4" t="n">
         <v>16.5</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>38.6</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>31.2</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>33.7</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>23.07060755336617</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>14.32</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>14.16307471264368</v>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -599,27 +603,29 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>64</v>
+      </c>
+      <c r="D5" t="n">
         <v>12.4</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>31</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>27.6</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>28.8</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>14.90353037766831</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>12.54333333333333</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10.7602969348659</v>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -639,27 +645,29 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>64</v>
+      </c>
+      <c r="D6" t="n">
         <v>17.9</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>41.4</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>32.7</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>35.7</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>23.04187192118227</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>16.85166666666667</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>15.67289272030651</v>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -679,27 +687,29 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>64</v>
+      </c>
+      <c r="D7" t="n">
         <v>7.7</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>23.8</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>21</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>22</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>9.35960591133005</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>9.313333333333334</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>5.597461685823755</v>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -719,27 +729,29 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>64</v>
+      </c>
+      <c r="D8" t="n">
         <v>16.7</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>38.3</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>29.5</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>32.5</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>19.97742200328407</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>17.52333333333333</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>14.19300766283525</v>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -759,27 +771,29 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>64</v>
+      </c>
+      <c r="D9" t="n">
         <v>17.5</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>40.8</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>31.7</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>34.8</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>23.44211822660099</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>15.17</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>15.62140804597701</v>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -799,27 +813,29 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>64</v>
+      </c>
+      <c r="D10" t="n">
         <v>17.3</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>40.9</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>31.4</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>34.7</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>22.7216748768473</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>15.87666666666667</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>15.24664750957854</v>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -839,27 +855,29 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>64</v>
+      </c>
+      <c r="D11" t="n">
         <v>18.3</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>38.4</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>34.9</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>36.1</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>23.3128078817734</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>17.67333333333333</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>15.75311302681992</v>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -879,27 +897,29 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>64</v>
+      </c>
+      <c r="D12" t="n">
         <v>26.3</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>48.4</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>42.3</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>44.4</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>32.60057471264368</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>25.37833333333333</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>23.35727969348659</v>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -917,27 +937,29 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>64</v>
+      </c>
+      <c r="D13" t="n">
         <v>10.5</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>27.8</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>23.6</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>25</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>13.5919540229885</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>10.99333333333333</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>8.291427203065133</v>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -955,27 +977,29 @@
         </is>
       </c>
       <c r="C14" t="n">
+        <v>64</v>
+      </c>
+      <c r="D14" t="n">
         <v>15.3</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>38.8</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>28.6</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>32.1</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>20.38793103448276</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>14.755</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>12.72509578544061</v>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -993,27 +1017,29 @@
         </is>
       </c>
       <c r="C15" t="n">
+        <v>64</v>
+      </c>
+      <c r="D15" t="n">
         <v>14</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>33.3</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>28.7</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>30.2</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>17.28858784893268</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>13.04</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>12.86278735632184</v>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1031,27 +1057,29 @@
         </is>
       </c>
       <c r="C16" t="n">
+        <v>64</v>
+      </c>
+      <c r="D16" t="n">
         <v>21.8</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>45.5</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>36.1</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>39.3</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>26.12068965517241</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>20.37333333333333</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>20.29214559386973</v>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1069,27 +1097,29 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>64</v>
+      </c>
+      <c r="D17" t="n">
         <v>9.9</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>27.2</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>23.9</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>25</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>13.88957307060755</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>9.986666666666666</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>7.44492337164751</v>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1107,27 +1137,29 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>64</v>
+      </c>
+      <c r="D18" t="n">
         <v>14.6</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>36.2</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>29.4</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>31.7</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>20.43513957307061</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>12.75666666666667</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>12.45450191570881</v>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1145,27 +1177,29 @@
         </is>
       </c>
       <c r="C19" t="n">
+        <v>64</v>
+      </c>
+      <c r="D19" t="n">
         <v>11.2</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>30.2</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>24.8</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>26.7</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>15.70607553366174</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>9.948333333333334</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>9.539032567049809</v>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1183,27 +1217,29 @@
         </is>
       </c>
       <c r="C20" t="n">
+        <v>64</v>
+      </c>
+      <c r="D20" t="n">
         <v>16.1</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>39.1</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>29.9</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>33.1</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>22.47536945812808</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>13.71333333333333</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>14.2073754789272</v>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1221,27 +1257,29 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>64</v>
+      </c>
+      <c r="D21" t="n">
         <v>8</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>23</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>20.6</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>21.4</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>11.0940065681445</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>7.748333333333333</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>6.460727969348659</v>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1259,27 +1297,29 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>64</v>
+      </c>
+      <c r="D22" t="n">
         <v>15.5</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>37.4</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>30.5</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>32.8</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>21.21510673234811</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>13.87666666666667</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>13.31058429118774</v>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1297,27 +1337,29 @@
         </is>
       </c>
       <c r="C23" t="n">
+        <v>64</v>
+      </c>
+      <c r="D23" t="n">
         <v>15.5</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>37.5</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>31.3</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>33.4</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>18.3435960591133</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>14.23166666666667</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>14.68989463601532</v>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1335,27 +1377,29 @@
         </is>
       </c>
       <c r="C24" t="n">
+        <v>64</v>
+      </c>
+      <c r="D24" t="n">
         <v>21.8</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>47.2</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>37.4</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>40.7</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>25.66091954022989</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>22.31166666666667</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>19.2397030651341</v>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1371,27 +1415,29 @@
         </is>
       </c>
       <c r="C25" t="n">
+        <v>64</v>
+      </c>
+      <c r="D25" t="n">
         <v>15.1</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>33.6</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>31</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>31.9</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>20.39819376026272</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>12.99666666666667</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>13.60392720306514</v>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1407,27 +1453,29 @@
         </is>
       </c>
       <c r="C26" t="n">
+        <v>64</v>
+      </c>
+      <c r="D26" t="n">
         <v>19</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>41.9</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>35.3</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>37.6</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>22.76067323481117</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>16.95833333333333</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>18.21000957854406</v>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1445,27 +1493,29 @@
         </is>
       </c>
       <c r="C27" t="n">
+        <v>64</v>
+      </c>
+      <c r="D27" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>26.4</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>23.6</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>24.6</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>12.4692118226601</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>10</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>8.045977011494253</v>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -1483,27 +1533,29 @@
         </is>
       </c>
       <c r="C28" t="n">
+        <v>64</v>
+      </c>
+      <c r="D28" t="n">
         <v>14.3</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>36.5</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>27</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>30.2</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>18.05829228243022</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>12.725</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>13.13697318007663</v>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1521,27 +1573,29 @@
         </is>
       </c>
       <c r="C29" t="n">
+        <v>64</v>
+      </c>
+      <c r="D29" t="n">
         <v>10.2</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>26.8</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>24.2</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>25.1</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>14.46018062397373</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>9.675000000000001</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>8.080699233716475</v>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -1559,27 +1613,29 @@
         </is>
       </c>
       <c r="C30" t="n">
+        <v>64</v>
+      </c>
+      <c r="D30" t="n">
         <v>13.7</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>36.2</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>27.7</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>30.6</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>19.04556650246305</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>12.21833333333333</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>11.72892720306513</v>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1596,27 +1652,29 @@
         </is>
       </c>
       <c r="C31" t="n">
+        <v>64</v>
+      </c>
+      <c r="D31" t="n">
         <v>7.4</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>21</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>19.3</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>19.9</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>12.8427750410509</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>5.658333333333333</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>5.483716475095785</v>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -1633,27 +1691,29 @@
         </is>
       </c>
       <c r="C32" t="n">
+        <v>64</v>
+      </c>
+      <c r="D32" t="n">
         <v>9.4</v>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>27.4</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>22.1</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>23.9</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>16.04269293924466</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>6.86</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>7.224616858237548</v>
       </c>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1671,23 +1731,31 @@
 max_tokens: 1024</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>在推</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>H20_2</t>
-        </is>
-      </c>
+      <c r="C33" t="n">
+        <v>64</v>
+      </c>
+      <c r="D33" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="F33" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G33" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>15.49261083743842</v>
+      </c>
+      <c r="I33" t="n">
+        <v>11.09666666666667</v>
+      </c>
+      <c r="J33" t="n">
+        <v>9.256465517241379</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1704,23 +1772,31 @@
 max_tokens: 1024</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>在推</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>H20_3</t>
-        </is>
-      </c>
+      <c r="C34" t="n">
+        <v>64</v>
+      </c>
+      <c r="D34" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E34" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="G34" t="n">
+        <v>35</v>
+      </c>
+      <c r="H34" t="n">
+        <v>23.20812807881773</v>
+      </c>
+      <c r="I34" t="n">
+        <v>14.12333333333333</v>
+      </c>
+      <c r="J34" t="n">
+        <v>17.18031609195402</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1737,27 +1813,29 @@
         </is>
       </c>
       <c r="C35" t="n">
+        <v>64</v>
+      </c>
+      <c r="D35" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="D35" t="n">
+      <c r="E35" t="n">
         <v>27.4</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>24.3</v>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="n">
         <v>25.3</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>14.63875205254516</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>9.896666666666667</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>6.791187739463602</v>
       </c>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -1775,27 +1853,29 @@
         </is>
       </c>
       <c r="C36" t="n">
+        <v>64</v>
+      </c>
+      <c r="D36" t="n">
         <v>14.6</v>
       </c>
-      <c r="D36" t="n">
+      <c r="E36" t="n">
         <v>37.4</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>28.7</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>31.7</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>21.15968801313629</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>13.60666666666667</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>11.40325670498084</v>
       </c>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -1832,27 +1912,29 @@
         </is>
       </c>
       <c r="C38" t="n">
+        <v>64</v>
+      </c>
+      <c r="D38" t="n">
         <v>11.2</v>
       </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
         <v>24.5</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>26.3</v>
       </c>
-      <c r="F38" t="n">
+      <c r="G38" t="n">
         <v>25.7</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>14.56896551724138</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>11.45333333333333</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>9.052921455938696</v>
       </c>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -1872,27 +1954,29 @@
         </is>
       </c>
       <c r="C39" t="n">
+        <v>64</v>
+      </c>
+      <c r="D39" t="n">
         <v>18.8</v>
       </c>
-      <c r="D39" t="n">
+      <c r="E39" t="n">
         <v>39.1</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>33.8</v>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>35.6</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>24.85837438423645</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>18.93833333333333</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>15.12811302681992</v>
       </c>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
@@ -1912,27 +1996,29 @@
         </is>
       </c>
       <c r="C40" t="n">
+        <v>64</v>
+      </c>
+      <c r="D40" t="n">
         <v>12.2</v>
       </c>
-      <c r="D40" t="n">
+      <c r="E40" t="n">
         <v>27.3</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>26.5</v>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="n">
         <v>26.8</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>14.85426929392447</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>12.51333333333333</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>10.51125478927203</v>
       </c>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
@@ -1952,27 +2038,29 @@
         </is>
       </c>
       <c r="C41" t="n">
+        <v>64</v>
+      </c>
+      <c r="D41" t="n">
         <v>20.3</v>
       </c>
-      <c r="D41" t="n">
+      <c r="E41" t="n">
         <v>42.7</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>34.4</v>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>37.2</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>24.10919540229885</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>20.23333333333333</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>18.07710727969349</v>
       </c>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -1992,27 +2080,29 @@
         </is>
       </c>
       <c r="C42" t="n">
+        <v>64</v>
+      </c>
+      <c r="D42" t="n">
         <v>12.3</v>
       </c>
-      <c r="D42" t="n">
+      <c r="E42" t="n">
         <v>29.76</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>27.65</v>
       </c>
-      <c r="F42" t="n">
+      <c r="G42" t="n">
         <v>28.37</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>14.72906403940887</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>12.33666666666667</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>10.85727969348659</v>
       </c>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -2032,27 +2122,29 @@
         </is>
       </c>
       <c r="C43" t="n">
+        <v>64</v>
+      </c>
+      <c r="D43" t="n">
         <v>18</v>
       </c>
-      <c r="D43" t="n">
+      <c r="E43" t="n">
         <v>39.1</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>31.1</v>
       </c>
-      <c r="F43" t="n">
+      <c r="G43" t="n">
         <v>33.8</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>20.01231527093596</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>20.915</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>14.69827586206897</v>
       </c>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -2069,27 +2161,29 @@
         </is>
       </c>
       <c r="C44" t="n">
+        <v>64</v>
+      </c>
+      <c r="D44" t="n">
         <v>18.5</v>
       </c>
-      <c r="D44" t="n">
+      <c r="E44" t="n">
         <v>41.4</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>33.4</v>
       </c>
-      <c r="F44" t="n">
+      <c r="G44" t="n">
         <v>36.1</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>25.56444991789821</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>14.96666666666667</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>16.94324712643678</v>
       </c>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
@@ -2106,27 +2200,29 @@
         </is>
       </c>
       <c r="C45" t="n">
+        <v>64</v>
+      </c>
+      <c r="D45" t="n">
         <v>19.9</v>
       </c>
-      <c r="D45" t="n">
+      <c r="E45" t="n">
         <v>44.8</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>34.6</v>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
         <v>38.1</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>26.92118226600986</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>17.7</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>17.29645593869731</v>
       </c>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -2146,27 +2242,29 @@
         </is>
       </c>
       <c r="C46" t="n">
+        <v>64</v>
+      </c>
+      <c r="D46" t="n">
         <v>15.7</v>
       </c>
-      <c r="D46" t="n">
+      <c r="E46" t="n">
         <v>35.7</v>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>31.6</v>
       </c>
-      <c r="F46" t="n">
+      <c r="G46" t="n">
         <v>33</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>18.80541871921182</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>16.50833333333333</v>
       </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
         <v>13.31657088122605</v>
       </c>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -2186,27 +2284,29 @@
         </is>
       </c>
       <c r="C47" t="n">
+        <v>64</v>
+      </c>
+      <c r="D47" t="n">
         <v>25.8</v>
       </c>
-      <c r="D47" t="n">
+      <c r="E47" t="n">
         <v>49.9</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>40.6</v>
       </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
         <v>43.8</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>30.29967159277504</v>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>27.01166666666667</v>
       </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
         <v>22.29286398467433</v>
       </c>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -2222,29 +2322,31 @@
         </is>
       </c>
       <c r="C48" t="n">
+        <v>64</v>
+      </c>
+      <c r="D48" t="n">
         <v>11.9</v>
       </c>
-      <c r="D48" t="n">
+      <c r="E48" t="n">
         <v>29.9</v>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>25/62</t>
         </is>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>27.1</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>17.71551724137931</v>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>11.92</v>
       </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
         <v>8.526101532567051</v>
       </c>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -2260,27 +2362,29 @@
         </is>
       </c>
       <c r="C49" t="n">
+        <v>64</v>
+      </c>
+      <c r="D49" t="n">
         <v>15.9</v>
       </c>
-      <c r="D49" t="n">
+      <c r="E49" t="n">
         <v>37.1</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>30.6</v>
       </c>
-      <c r="F49" t="n">
+      <c r="G49" t="n">
         <v>32.8</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>21.97249589490969</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>15.45833333333333</v>
       </c>
-      <c r="I49" t="n">
+      <c r="J49" t="n">
         <v>12.63050766283525</v>
       </c>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
@@ -2299,27 +2403,29 @@
         </is>
       </c>
       <c r="C50" t="n">
+        <v>64</v>
+      </c>
+      <c r="D50" t="n">
         <v>11.7</v>
       </c>
-      <c r="D50" t="n">
+      <c r="E50" t="n">
         <v>29.4</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>26.3</v>
       </c>
-      <c r="F50" t="n">
+      <c r="G50" t="n">
         <v>27.4</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>15.19293924466338</v>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>11.90166666666667</v>
       </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
         <v>9.47198275862069</v>
       </c>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
@@ -2338,27 +2444,29 @@
         </is>
       </c>
       <c r="C51" t="n">
+        <v>64</v>
+      </c>
+      <c r="D51" t="n">
         <v>18.6</v>
       </c>
-      <c r="D51" t="n">
+      <c r="E51" t="n">
         <v>41.3</v>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>33</v>
       </c>
-      <c r="F51" t="n">
+      <c r="G51" t="n">
         <v>35.8</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>23.17733990147783</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>18.515</v>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
         <v>16.05004789272031</v>
       </c>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
@@ -2376,14 +2484,30 @@
 num_frames: 64</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="C52" t="n">
+        <v>64</v>
+      </c>
+      <c r="D52" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="E52" t="n">
+        <v>24</v>
+      </c>
+      <c r="F52" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="G52" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="H52" t="n">
+        <v>13.05829228243021</v>
+      </c>
+      <c r="I52" t="n">
+        <v>8.783333333333333</v>
+      </c>
+      <c r="J52" t="n">
+        <v>7.397030651340995</v>
+      </c>
       <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -2401,14 +2525,30 @@
 num_frames: 64</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="C53" t="n">
+        <v>64</v>
+      </c>
+      <c r="D53" t="n">
+        <v>15</v>
+      </c>
+      <c r="E53" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="F53" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="H53" t="n">
+        <v>19.50738916256158</v>
+      </c>
+      <c r="I53" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="J53" t="n">
+        <v>13.25311302681992</v>
+      </c>
       <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -2426,14 +2566,30 @@
 num_frames: 64</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="C54" t="n">
+        <v>64</v>
+      </c>
+      <c r="D54" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E54" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="F54" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="G54" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="H54" t="n">
+        <v>16.33620689655172</v>
+      </c>
+      <c r="I54" t="n">
+        <v>13.42166666666667</v>
+      </c>
+      <c r="J54" t="n">
+        <v>11.19492337164751</v>
+      </c>
       <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -2451,14 +2607,30 @@
 num_frames: 64</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+      <c r="C55" t="n">
+        <v>64</v>
+      </c>
+      <c r="D55" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="E55" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="F55" t="n">
+        <v>37</v>
+      </c>
+      <c r="G55" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>25.73481116584565</v>
+      </c>
+      <c r="I55" t="n">
+        <v>21.71833333333333</v>
+      </c>
+      <c r="J55" t="n">
+        <v>18.24233716475096</v>
+      </c>
       <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -2476,14 +2648,32 @@
 num_frames: 64</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="C56" t="n">
+        <v>64</v>
+      </c>
+      <c r="D56" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>28..57</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="G56" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>15.86822660098522</v>
+      </c>
+      <c r="I56" t="n">
+        <v>13.00166666666667</v>
+      </c>
+      <c r="J56" t="n">
+        <v>9.465996168582375</v>
+      </c>
       <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -2501,14 +2691,30 @@
 num_frames: 64</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="C57" t="n">
+        <v>64</v>
+      </c>
+      <c r="D57" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F57" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="H57" t="n">
+        <v>27.05870279146141</v>
+      </c>
+      <c r="I57" t="n">
+        <v>18.885</v>
+      </c>
+      <c r="J57" t="n">
+        <v>17.01628352490421</v>
+      </c>
       <c r="K57" t="inlineStr"/>
     </row>
   </sheetData>

--- a/figs/exps/performance_parsed.xlsx
+++ b/figs/exps/performance_parsed.xlsx
@@ -525,10 +525,10 @@
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>29.6</v>
+        <v>8.945360195360196</v>
       </c>
       <c r="F3" t="n">
-        <v>25.1</v>
+        <v>12.109375</v>
       </c>
       <c r="G3" t="n">
         <v>26.6</v>
@@ -567,10 +567,10 @@
         <v>16.5</v>
       </c>
       <c r="E4" t="n">
-        <v>38.6</v>
+        <v>15.99664224664225</v>
       </c>
       <c r="F4" t="n">
-        <v>31.2</v>
+        <v>16.71401515151515</v>
       </c>
       <c r="G4" t="n">
         <v>33.7</v>
@@ -609,10 +609,10 @@
         <v>12.4</v>
       </c>
       <c r="E5" t="n">
-        <v>31</v>
+        <v>9.339133089133089</v>
       </c>
       <c r="F5" t="n">
-        <v>27.6</v>
+        <v>13.93229166666667</v>
       </c>
       <c r="G5" t="n">
         <v>28.8</v>
@@ -651,10 +651,10 @@
         <v>17.9</v>
       </c>
       <c r="E6" t="n">
-        <v>41.4</v>
+        <v>17.44810744810745</v>
       </c>
       <c r="F6" t="n">
-        <v>32.7</v>
+        <v>18.14630681818182</v>
       </c>
       <c r="G6" t="n">
         <v>35.7</v>
@@ -693,10 +693,10 @@
         <v>7.7</v>
       </c>
       <c r="E7" t="n">
-        <v>23.8</v>
+        <v>5.086996336996337</v>
       </c>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>9.067234848484848</v>
       </c>
       <c r="G7" t="n">
         <v>22</v>
@@ -735,10 +735,10 @@
         <v>16.7</v>
       </c>
       <c r="E8" t="n">
-        <v>38.3</v>
+        <v>18.13339438339439</v>
       </c>
       <c r="F8" t="n">
-        <v>29.5</v>
+        <v>15.95643939393939</v>
       </c>
       <c r="G8" t="n">
         <v>32.5</v>
@@ -777,10 +777,10 @@
         <v>17.5</v>
       </c>
       <c r="E9" t="n">
-        <v>40.8</v>
+        <v>18.10897435897436</v>
       </c>
       <c r="F9" t="n">
-        <v>31.7</v>
+        <v>17.12831439393939</v>
       </c>
       <c r="G9" t="n">
         <v>34.8</v>
@@ -819,10 +819,10 @@
         <v>17.3</v>
       </c>
       <c r="E10" t="n">
-        <v>40.9</v>
+        <v>18.45238095238096</v>
       </c>
       <c r="F10" t="n">
-        <v>31.4</v>
+        <v>16.76136363636364</v>
       </c>
       <c r="G10" t="n">
         <v>34.7</v>
@@ -861,10 +861,10 @@
         <v>18.3</v>
       </c>
       <c r="E11" t="n">
-        <v>38.4</v>
+        <v>14.90995115995116</v>
       </c>
       <c r="F11" t="n">
-        <v>34.9</v>
+        <v>20.00473484848485</v>
       </c>
       <c r="G11" t="n">
         <v>36.1</v>
@@ -903,10 +903,10 @@
         <v>26.3</v>
       </c>
       <c r="E12" t="n">
-        <v>48.4</v>
+        <v>24.78327228327228</v>
       </c>
       <c r="F12" t="n">
-        <v>42.3</v>
+        <v>27.13068181818182</v>
       </c>
       <c r="G12" t="n">
         <v>44.4</v>
@@ -943,10 +943,10 @@
         <v>10.5</v>
       </c>
       <c r="E13" t="n">
-        <v>27.8</v>
+        <v>9.154456654456654</v>
       </c>
       <c r="F13" t="n">
-        <v>23.6</v>
+        <v>11.1624053030303</v>
       </c>
       <c r="G13" t="n">
         <v>25</v>
@@ -983,10 +983,10 @@
         <v>15.3</v>
       </c>
       <c r="E14" t="n">
-        <v>38.8</v>
+        <v>16.18437118437118</v>
       </c>
       <c r="F14" t="n">
-        <v>28.6</v>
+        <v>14.84375</v>
       </c>
       <c r="G14" t="n">
         <v>32.1</v>
@@ -1023,10 +1023,10 @@
         <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>33.3</v>
+        <v>12.5534188034188</v>
       </c>
       <c r="F15" t="n">
-        <v>28.7</v>
+        <v>14.80823863636364</v>
       </c>
       <c r="G15" t="n">
         <v>30.2</v>
@@ -1063,10 +1063,10 @@
         <v>21.8</v>
       </c>
       <c r="E16" t="n">
-        <v>45.5</v>
+        <v>23.28754578754579</v>
       </c>
       <c r="F16" t="n">
-        <v>36.1</v>
+        <v>21.02272727272727</v>
       </c>
       <c r="G16" t="n">
         <v>39.3</v>
@@ -1103,10 +1103,10 @@
         <v>9.9</v>
       </c>
       <c r="E17" t="n">
-        <v>27.2</v>
+        <v>7.168803418803419</v>
       </c>
       <c r="F17" t="n">
-        <v>23.9</v>
+        <v>11.26893939393939</v>
       </c>
       <c r="G17" t="n">
         <v>25</v>
@@ -1143,10 +1143,10 @@
         <v>14.6</v>
       </c>
       <c r="E18" t="n">
-        <v>36.2</v>
+        <v>13.95299145299145</v>
       </c>
       <c r="F18" t="n">
-        <v>29.4</v>
+        <v>14.89109848484848</v>
       </c>
       <c r="G18" t="n">
         <v>31.7</v>
@@ -1183,10 +1183,10 @@
         <v>11.2</v>
       </c>
       <c r="E19" t="n">
-        <v>30.2</v>
+        <v>9.642857142857142</v>
       </c>
       <c r="F19" t="n">
-        <v>24.8</v>
+        <v>12.05018939393939</v>
       </c>
       <c r="G19" t="n">
         <v>26.7</v>
@@ -1223,10 +1223,10 @@
         <v>16.1</v>
       </c>
       <c r="E20" t="n">
-        <v>39.1</v>
+        <v>16.33699633699634</v>
       </c>
       <c r="F20" t="n">
-        <v>29.9</v>
+        <v>16.05113636363636</v>
       </c>
       <c r="G20" t="n">
         <v>33.1</v>
@@ -1263,10 +1263,10 @@
         <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>23</v>
+        <v>5.952380952380953</v>
       </c>
       <c r="F21" t="n">
-        <v>20.6</v>
+        <v>9.114583333333334</v>
       </c>
       <c r="G21" t="n">
         <v>21.4</v>
@@ -1303,10 +1303,10 @@
         <v>15.5</v>
       </c>
       <c r="E22" t="n">
-        <v>37.4</v>
+        <v>15.25335775335775</v>
       </c>
       <c r="F22" t="n">
-        <v>30.5</v>
+        <v>15.61316287878788</v>
       </c>
       <c r="G22" t="n">
         <v>32.8</v>
@@ -1343,10 +1343,10 @@
         <v>15.5</v>
       </c>
       <c r="E23" t="n">
-        <v>37.5</v>
+        <v>13.66758241758242</v>
       </c>
       <c r="F23" t="n">
-        <v>31.3</v>
+        <v>16.40625</v>
       </c>
       <c r="G23" t="n">
         <v>33.4</v>
@@ -1383,10 +1383,10 @@
         <v>21.8</v>
       </c>
       <c r="E24" t="n">
-        <v>47.2</v>
+        <v>22.25732600732601</v>
       </c>
       <c r="F24" t="n">
-        <v>37.4</v>
+        <v>21.60274621212121</v>
       </c>
       <c r="G24" t="n">
         <v>40.7</v>
@@ -1421,10 +1421,10 @@
         <v>15.1</v>
       </c>
       <c r="E25" t="n">
-        <v>33.6</v>
+        <v>12.4969474969475</v>
       </c>
       <c r="F25" t="n">
-        <v>31</v>
+        <v>16.50094696969697</v>
       </c>
       <c r="G25" t="n">
         <v>31.9</v>
@@ -1459,10 +1459,10 @@
         <v>19</v>
       </c>
       <c r="E26" t="n">
-        <v>41.9</v>
+        <v>17.89224664224664</v>
       </c>
       <c r="F26" t="n">
-        <v>35.3</v>
+        <v>19.53125</v>
       </c>
       <c r="G26" t="n">
         <v>37.6</v>
@@ -1499,10 +1499,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>26.4</v>
+        <v>7.509157509157509</v>
       </c>
       <c r="F27" t="n">
-        <v>23.6</v>
+        <v>10.94933712121212</v>
       </c>
       <c r="G27" t="n">
         <v>24.6</v>
@@ -1539,10 +1539,10 @@
         <v>14.3</v>
       </c>
       <c r="E28" t="n">
-        <v>36.5</v>
+        <v>15.4532967032967</v>
       </c>
       <c r="F28" t="n">
-        <v>27</v>
+        <v>13.63636363636364</v>
       </c>
       <c r="G28" t="n">
         <v>30.2</v>
@@ -1579,10 +1579,10 @@
         <v>10.2</v>
       </c>
       <c r="E29" t="n">
-        <v>26.8</v>
+        <v>7.477106227106227</v>
       </c>
       <c r="F29" t="n">
-        <v>24.2</v>
+        <v>11.60037878787879</v>
       </c>
       <c r="G29" t="n">
         <v>25.1</v>
@@ -1619,10 +1619,10 @@
         <v>13.7</v>
       </c>
       <c r="E30" t="n">
-        <v>36.2</v>
+        <v>12.87545787545788</v>
       </c>
       <c r="F30" t="n">
-        <v>27.7</v>
+        <v>14.18087121212121</v>
       </c>
       <c r="G30" t="n">
         <v>30.6</v>
@@ -1658,10 +1658,10 @@
         <v>7.4</v>
       </c>
       <c r="E31" t="n">
-        <v>21</v>
+        <v>5.123626373626373</v>
       </c>
       <c r="F31" t="n">
-        <v>19.3</v>
+        <v>8.581912878787879</v>
       </c>
       <c r="G31" t="n">
         <v>19.9</v>
@@ -1697,10 +1697,10 @@
         <v>9.4</v>
       </c>
       <c r="E32" t="n">
-        <v>27.4</v>
+        <v>7.571733821733822</v>
       </c>
       <c r="F32" t="n">
-        <v>22.1</v>
+        <v>10.26278409090909</v>
       </c>
       <c r="G32" t="n">
         <v>23.9</v>
@@ -1738,10 +1738,10 @@
         <v>11.4</v>
       </c>
       <c r="E33" t="n">
-        <v>28.8</v>
+        <v>8.504273504273504</v>
       </c>
       <c r="F33" t="n">
-        <v>26.3</v>
+        <v>12.91429924242424</v>
       </c>
       <c r="G33" t="n">
         <v>27.1</v>
@@ -1779,10 +1779,10 @@
         <v>17.8</v>
       </c>
       <c r="E34" t="n">
-        <v>40.1</v>
+        <v>17.86477411477411</v>
       </c>
       <c r="F34" t="n">
-        <v>32.3</v>
+        <v>17.69649621212121</v>
       </c>
       <c r="G34" t="n">
         <v>35</v>
@@ -1819,10 +1819,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>27.4</v>
+        <v>6.466727716727717</v>
       </c>
       <c r="F35" t="n">
-        <v>24.3</v>
+        <v>11.44649621212121</v>
       </c>
       <c r="G35" t="n">
         <v>25.3</v>
@@ -1859,10 +1859,10 @@
         <v>14.6</v>
       </c>
       <c r="E36" t="n">
-        <v>37.4</v>
+        <v>14.36507936507936</v>
       </c>
       <c r="F36" t="n">
-        <v>28.7</v>
+        <v>14.66619318181818</v>
       </c>
       <c r="G36" t="n">
         <v>31.7</v>
@@ -1918,10 +1918,10 @@
         <v>11.2</v>
       </c>
       <c r="E38" t="n">
-        <v>24.5</v>
+        <v>7.380952380952381</v>
       </c>
       <c r="F38" t="n">
-        <v>26.3</v>
+        <v>13.17471590909091</v>
       </c>
       <c r="G38" t="n">
         <v>25.7</v>
@@ -1960,10 +1960,10 @@
         <v>18.8</v>
       </c>
       <c r="E39" t="n">
-        <v>39.1</v>
+        <v>17.61141636141636</v>
       </c>
       <c r="F39" t="n">
-        <v>33.8</v>
+        <v>19.38920454545455</v>
       </c>
       <c r="G39" t="n">
         <v>35.6</v>
@@ -2002,10 +2002,10 @@
         <v>12.2</v>
       </c>
       <c r="E40" t="n">
-        <v>27.3</v>
+        <v>9.438339438339439</v>
       </c>
       <c r="F40" t="n">
-        <v>26.5</v>
+        <v>13.68371212121212</v>
       </c>
       <c r="G40" t="n">
         <v>26.8</v>
@@ -2044,10 +2044,10 @@
         <v>20.3</v>
       </c>
       <c r="E41" t="n">
-        <v>42.7</v>
+        <v>20.94627594627595</v>
       </c>
       <c r="F41" t="n">
-        <v>34.4</v>
+        <v>19.93371212121212</v>
       </c>
       <c r="G41" t="n">
         <v>37.2</v>
@@ -2086,10 +2086,10 @@
         <v>12.3</v>
       </c>
       <c r="E42" t="n">
-        <v>29.76</v>
+        <v>9.578754578754578</v>
       </c>
       <c r="F42" t="n">
-        <v>27.65</v>
+        <v>13.70738636363636</v>
       </c>
       <c r="G42" t="n">
         <v>28.37</v>
@@ -2128,10 +2128,10 @@
         <v>18</v>
       </c>
       <c r="E43" t="n">
-        <v>39.1</v>
+        <v>19.39102564102564</v>
       </c>
       <c r="F43" t="n">
-        <v>31.1</v>
+        <v>17.25852272727273</v>
       </c>
       <c r="G43" t="n">
         <v>33.8</v>
@@ -2167,10 +2167,10 @@
         <v>18.5</v>
       </c>
       <c r="E44" t="n">
-        <v>41.4</v>
+        <v>17.98076923076923</v>
       </c>
       <c r="F44" t="n">
-        <v>33.4</v>
+        <v>18.78551136363636</v>
       </c>
       <c r="G44" t="n">
         <v>36.1</v>
@@ -2206,10 +2206,10 @@
         <v>19.9</v>
       </c>
       <c r="E45" t="n">
-        <v>44.8</v>
+        <v>20.34035409035409</v>
       </c>
       <c r="F45" t="n">
-        <v>34.6</v>
+        <v>19.61410984848485</v>
       </c>
       <c r="G45" t="n">
         <v>38.1</v>
@@ -2248,10 +2248,10 @@
         <v>15.7</v>
       </c>
       <c r="E46" t="n">
-        <v>35.7</v>
+        <v>12.67399267399267</v>
       </c>
       <c r="F46" t="n">
-        <v>31.6</v>
+        <v>17.27035984848485</v>
       </c>
       <c r="G46" t="n">
         <v>33</v>
@@ -2290,10 +2290,10 @@
         <v>25.8</v>
       </c>
       <c r="E47" t="n">
-        <v>49.9</v>
+        <v>26.0958485958486</v>
       </c>
       <c r="F47" t="n">
-        <v>40.6</v>
+        <v>25.63920454545455</v>
       </c>
       <c r="G47" t="n">
         <v>43.8</v>
@@ -2328,12 +2328,10 @@
         <v>11.9</v>
       </c>
       <c r="E48" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>25/62</t>
-        </is>
+        <v>9.797008547008547</v>
+      </c>
+      <c r="F48" t="n">
+        <v>13.00899621212121</v>
       </c>
       <c r="G48" t="n">
         <v>27.1</v>
@@ -2368,10 +2366,10 @@
         <v>15.9</v>
       </c>
       <c r="E49" t="n">
-        <v>37.1</v>
+        <v>15.20757020757021</v>
       </c>
       <c r="F49" t="n">
-        <v>30.6</v>
+        <v>16.22869318181818</v>
       </c>
       <c r="G49" t="n">
         <v>32.8</v>
@@ -2409,10 +2407,10 @@
         <v>11.7</v>
       </c>
       <c r="E50" t="n">
-        <v>29.4</v>
+        <v>9.407814407814408</v>
       </c>
       <c r="F50" t="n">
-        <v>26.3</v>
+        <v>12.85511363636364</v>
       </c>
       <c r="G50" t="n">
         <v>27.4</v>
@@ -2450,10 +2448,10 @@
         <v>18.6</v>
       </c>
       <c r="E51" t="n">
-        <v>41.3</v>
+        <v>19.3009768009768</v>
       </c>
       <c r="F51" t="n">
-        <v>33</v>
+        <v>18.27651515151515</v>
       </c>
       <c r="G51" t="n">
         <v>35.8</v>
@@ -2491,10 +2489,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>24</v>
+        <v>6.578144078144079</v>
       </c>
       <c r="F52" t="n">
-        <v>22.6</v>
+        <v>10.65340909090909</v>
       </c>
       <c r="G52" t="n">
         <v>23.1</v>
@@ -2532,10 +2530,10 @@
         <v>15</v>
       </c>
       <c r="E53" t="n">
-        <v>36.3</v>
+        <v>15.30067155067155</v>
       </c>
       <c r="F53" t="n">
-        <v>29.1</v>
+        <v>14.77272727272727</v>
       </c>
       <c r="G53" t="n">
         <v>31.5</v>
@@ -2573,10 +2571,10 @@
         <v>13.2</v>
       </c>
       <c r="E54" t="n">
-        <v>29.9</v>
+        <v>10.64102564102564</v>
       </c>
       <c r="F54" t="n">
-        <v>28.4</v>
+        <v>14.51231060606061</v>
       </c>
       <c r="G54" t="n">
         <v>28.9</v>
@@ -2614,10 +2612,10 @@
         <v>21.2</v>
       </c>
       <c r="E55" t="n">
-        <v>44.4</v>
+        <v>20.29151404151404</v>
       </c>
       <c r="F55" t="n">
-        <v>37</v>
+        <v>21.7092803030303</v>
       </c>
       <c r="G55" t="n">
         <v>39.5</v>
@@ -2654,13 +2652,11 @@
       <c r="D56" t="n">
         <v>12.2</v>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>28..57</t>
-        </is>
+      <c r="E56" t="n">
+        <v>9.32997557997558</v>
       </c>
       <c r="F56" t="n">
-        <v>26.9</v>
+        <v>13.671875</v>
       </c>
       <c r="G56" t="n">
         <v>27.5</v>
@@ -2698,10 +2694,10 @@
         <v>20.1</v>
       </c>
       <c r="E57" t="n">
-        <v>42.5</v>
+        <v>18.6523199023199</v>
       </c>
       <c r="F57" t="n">
-        <v>36.1</v>
+        <v>20.91619318181818</v>
       </c>
       <c r="G57" t="n">
         <v>38.3</v>

--- a/figs/exps/performance_parsed.xlsx
+++ b/figs/exps/performance_parsed.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="13060"/>
+    <workbookView windowWidth="30240" windowHeight="13280"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="106">
   <si>
     <t>模型</t>
   </si>
@@ -244,6 +244,49 @@
     <t>Keye-VL-1_5-8B-sub</t>
   </si>
   <si>
+    <t>Qwen3.5-4B-Instruct</t>
+  </si>
+  <si>
+    <t>temperature=0.7, 
+max_new_tokens=40960,
+presence_penalty=1.5,
+top_p=0.8,
+top_k=20</t>
+  </si>
+  <si>
+    <t>Qwen3.5-4B-sub</t>
+  </si>
+  <si>
+    <t>Qwen3.5-9B</t>
+  </si>
+  <si>
+    <t>Qwen3.5-9B-sub</t>
+  </si>
+  <si>
+    <t>Qwen3.5-27B</t>
+  </si>
+  <si>
+    <t>Qwen3.5-27B-sub</t>
+  </si>
+  <si>
+    <t>Qwen3.5-A3B</t>
+  </si>
+  <si>
+    <t>Qwen3.5-A3B-sub</t>
+  </si>
+  <si>
+    <t>Qwen3.5-A10B</t>
+  </si>
+  <si>
+    <t>Qwen3.5-A10B-sub</t>
+  </si>
+  <si>
+    <t>Qwen3.5-A17B</t>
+  </si>
+  <si>
+    <t>Qwen3.5-A17B-sub</t>
+  </si>
+  <si>
     <t>Thinking Model</t>
   </si>
   <si>
@@ -364,6 +407,16 @@
   </si>
   <si>
     <t>GLM4.6-flash-sub</t>
+  </si>
+  <si>
+    <t>Qwen3.5-4B</t>
+  </si>
+  <si>
+    <t>temperature=1.0,
+top_p=0.95,
+top_k=20,
+presence_penalty=1.5,
+max_new_tokens=32768,</t>
   </si>
 </sst>
 </file>
@@ -1357,10 +1410,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="44.8653846153846" customWidth="1"/>
+    <col min="1" max="1" width="47.1057692307692" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -2698,31 +2751,31 @@
         <v>60</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
-      </c>
-      <c r="C39" t="s">
-        <v>12</v>
-      </c>
-      <c r="D39" t="s">
-        <v>12</v>
-      </c>
-      <c r="E39" t="s">
-        <v>12</v>
-      </c>
-      <c r="F39" t="s">
-        <v>12</v>
-      </c>
-      <c r="G39" t="s">
-        <v>12</v>
-      </c>
-      <c r="H39" t="s">
-        <v>12</v>
-      </c>
-      <c r="I39" t="s">
-        <v>12</v>
-      </c>
-      <c r="J39" t="s">
-        <v>12</v>
+        <v>61</v>
+      </c>
+      <c r="C39">
+        <v>64</v>
+      </c>
+      <c r="D39">
+        <v>9.5</v>
+      </c>
+      <c r="E39">
+        <v>9.06287069988138</v>
+      </c>
+      <c r="F39">
+        <v>9.77842003853565</v>
+      </c>
+      <c r="G39">
+        <v>24.1</v>
+      </c>
+      <c r="H39">
+        <v>11.876026272578</v>
+      </c>
+      <c r="I39">
+        <v>9.04451137884873</v>
+      </c>
+      <c r="J39">
+        <v>8.50215517241379</v>
       </c>
       <c r="K39" t="s">
         <v>12</v>
@@ -2730,34 +2783,34 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
+        <v>62</v>
+      </c>
+      <c r="B40" t="s">
         <v>61</v>
       </c>
-      <c r="B40" t="s">
-        <v>62</v>
-      </c>
       <c r="C40">
         <v>64</v>
       </c>
       <c r="D40">
-        <v>11.6</v>
+        <v>15.4</v>
       </c>
       <c r="E40">
-        <v>9.67674970344009</v>
+        <v>16.7378410438909</v>
       </c>
       <c r="F40">
-        <v>12.5842967244701</v>
+        <v>14.6194605009634</v>
       </c>
       <c r="G40">
-        <v>26.2</v>
+        <v>32.3</v>
       </c>
       <c r="H40">
-        <v>14.9794745484401</v>
+        <v>17.6313628899836</v>
       </c>
       <c r="I40">
-        <v>11.303547523427</v>
+        <v>16.0508701472557</v>
       </c>
       <c r="J40">
-        <v>9.75574712643678</v>
+        <v>13.5488505747126</v>
       </c>
       <c r="K40" t="s">
         <v>12</v>
@@ -2768,31 +2821,31 @@
         <v>63</v>
       </c>
       <c r="B41" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C41">
         <v>64</v>
       </c>
       <c r="D41">
-        <v>18.2</v>
+        <v>10.3</v>
       </c>
       <c r="E41">
-        <v>18.573546856465</v>
+        <v>9.87396204033215</v>
       </c>
       <c r="F41">
-        <v>17.9431599229287</v>
+        <v>10.597302504817</v>
       </c>
       <c r="G41">
-        <v>35.3</v>
+        <v>26</v>
       </c>
       <c r="H41">
-        <v>23.2676518883415</v>
+        <v>11.4552545155993</v>
       </c>
       <c r="I41">
-        <v>16.5779785809906</v>
+        <v>9.8661311914324</v>
       </c>
       <c r="J41">
-        <v>16.3230363984674</v>
+        <v>10.0359195402299</v>
       </c>
       <c r="K41" t="s">
         <v>12</v>
@@ -2803,31 +2856,31 @@
         <v>64</v>
       </c>
       <c r="B42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C42">
         <v>64</v>
       </c>
       <c r="D42">
-        <v>11.8</v>
+        <v>18.3</v>
       </c>
       <c r="E42">
-        <v>10.0177935943061</v>
+        <v>21.1936536180308</v>
       </c>
       <c r="F42">
-        <v>12.7288053949904</v>
+        <v>16.7148362235067</v>
       </c>
       <c r="G42">
-        <v>27</v>
+        <v>35.5</v>
       </c>
       <c r="H42">
-        <v>13.1055008210181</v>
+        <v>20.6814449917898</v>
       </c>
       <c r="I42">
-        <v>11.8457161981258</v>
+        <v>17.5937081659973</v>
       </c>
       <c r="J42">
-        <v>10.9518678160919</v>
+        <v>17.3886494252874</v>
       </c>
       <c r="K42" t="s">
         <v>12</v>
@@ -2838,31 +2891,31 @@
         <v>65</v>
       </c>
       <c r="B43" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C43">
         <v>64</v>
       </c>
       <c r="D43">
-        <v>19.7</v>
+        <v>14</v>
       </c>
       <c r="E43">
-        <v>20.5026690391459</v>
+        <v>12.5845195729537</v>
       </c>
       <c r="F43">
-        <v>19.1835260115607</v>
+        <v>14.7639691714836</v>
       </c>
       <c r="G43">
-        <v>37.2</v>
+        <v>31.7</v>
       </c>
       <c r="H43">
-        <v>23.8711001642036</v>
+        <v>15.8374384236453</v>
       </c>
       <c r="I43">
-        <v>19.243641231593</v>
+        <v>14.8226238286479</v>
       </c>
       <c r="J43">
-        <v>17.4712643678161</v>
+        <v>12.3359674329502</v>
       </c>
       <c r="K43" t="s">
         <v>12</v>
@@ -2873,31 +2926,31 @@
         <v>66</v>
       </c>
       <c r="B44" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C44">
         <v>64</v>
       </c>
       <c r="D44">
-        <v>13.5</v>
+        <v>23.9</v>
       </c>
       <c r="E44">
-        <v>12.4688612099644</v>
+        <v>24.8042704626335</v>
       </c>
       <c r="F44">
-        <v>14.1016377649326</v>
+        <v>23.4344894026975</v>
       </c>
       <c r="G44">
-        <v>29.4</v>
+        <v>41.9</v>
       </c>
       <c r="H44">
-        <v>17.4343185550082</v>
+        <v>28.9244663382594</v>
       </c>
       <c r="I44">
-        <v>13.7198795180723</v>
+        <v>23.2362784471218</v>
       </c>
       <c r="J44">
-        <v>11.1123084291188</v>
+        <v>21.4798850574713</v>
       </c>
       <c r="K44" t="s">
         <v>12</v>
@@ -2905,34 +2958,34 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B45" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C45">
         <v>64</v>
       </c>
       <c r="D45">
-        <v>21.1</v>
+        <v>11.3</v>
       </c>
       <c r="E45">
-        <v>22.5963819691578</v>
+        <v>9.40391459074733</v>
       </c>
       <c r="F45">
-        <v>20.2191714836224</v>
+        <v>12.3554913294798</v>
       </c>
       <c r="G45">
-        <v>38.6</v>
+        <v>28.6</v>
       </c>
       <c r="H45">
-        <v>26.9704433497537</v>
+        <v>13.6658456486043</v>
       </c>
       <c r="I45">
-        <v>21.0993975903614</v>
+        <v>11.3269745649264</v>
       </c>
       <c r="J45">
-        <v>17.5706417624521</v>
+        <v>9.94372605363985</v>
       </c>
       <c r="K45" t="s">
         <v>12</v>
@@ -2940,34 +2993,34 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B46" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C46">
         <v>64</v>
       </c>
       <c r="D46">
-        <v>17.7</v>
+        <v>19.9</v>
       </c>
       <c r="E46">
-        <v>18.4193357058126</v>
+        <v>22.7164887307236</v>
       </c>
       <c r="F46">
-        <v>17.2447013487476</v>
+        <v>18.4368978805395</v>
       </c>
       <c r="G46">
-        <v>35.8</v>
+        <v>36.9</v>
       </c>
       <c r="H46">
-        <v>23.5550082101806</v>
+        <v>24.2138752052545</v>
       </c>
       <c r="I46">
-        <v>15.4852744310576</v>
+        <v>18.6429049531459</v>
       </c>
       <c r="J46">
-        <v>15.7710727969349</v>
+        <v>18.3752394636015</v>
       </c>
       <c r="K46" t="s">
         <v>12</v>
@@ -2975,34 +3028,34 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B47" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C47">
         <v>64</v>
       </c>
       <c r="D47">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="E47">
-        <v>11.3804863582444</v>
+        <v>11.1165480427046</v>
       </c>
       <c r="F47">
-        <v>13.3068400770713</v>
+        <v>13.2947976878613</v>
       </c>
       <c r="G47">
-        <v>28.6</v>
+        <v>29.5</v>
       </c>
       <c r="H47">
-        <v>15.7984400656815</v>
+        <v>14.8440065681445</v>
       </c>
       <c r="I47">
-        <v>12.2740963855422</v>
+        <v>12.8999330655957</v>
       </c>
       <c r="J47">
-        <v>11.036877394636</v>
+        <v>10.9147509578544</v>
       </c>
       <c r="K47" t="s">
         <v>12</v>
@@ -3010,34 +3063,34 @@
     </row>
     <row r="48" spans="1:11">
       <c r="A48" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B48" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C48">
         <v>64</v>
       </c>
       <c r="D48">
-        <v>19.5</v>
+        <v>20.9</v>
       </c>
       <c r="E48">
-        <v>21.2396204033215</v>
+        <v>22.3917556346382</v>
       </c>
       <c r="F48">
-        <v>18.5934489402697</v>
+        <v>20.0867052023121</v>
       </c>
       <c r="G48">
-        <v>36.5</v>
+        <v>39.2</v>
       </c>
       <c r="H48">
-        <v>24.7229064039409</v>
+        <v>24.8604269293924</v>
       </c>
       <c r="I48">
-        <v>17.4866131191432</v>
+        <v>21.7921686746988</v>
       </c>
       <c r="J48">
-        <v>17.9465996168582</v>
+        <v>17.9430076628352</v>
       </c>
       <c r="K48" t="s">
         <v>12</v>
@@ -3045,34 +3098,34 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B49" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C49">
         <v>64</v>
       </c>
       <c r="D49">
-        <v>18.3</v>
+        <v>16.9</v>
       </c>
       <c r="E49">
-        <v>20.4314946619217</v>
+        <v>14.5981613285884</v>
       </c>
       <c r="F49">
-        <v>17.1242774566474</v>
+        <v>18.1719653179191</v>
       </c>
       <c r="G49">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H49">
-        <v>23.3025451559934</v>
+        <v>16.8247126436782</v>
       </c>
       <c r="I49">
-        <v>15.826639892905</v>
+        <v>18.0672690763052</v>
       </c>
       <c r="J49">
-        <v>17.1192528735632</v>
+        <v>16.147030651341</v>
       </c>
       <c r="K49" t="s">
         <v>12</v>
@@ -3080,34 +3133,34 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B50" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C50">
         <v>64</v>
       </c>
       <c r="D50">
-        <v>15.9</v>
+        <v>24.5</v>
       </c>
       <c r="E50">
-        <v>13.4386120996441</v>
+        <v>25.6731909845789</v>
       </c>
       <c r="F50">
-        <v>17.2326589595376</v>
+        <v>23.8921001926782</v>
       </c>
       <c r="G50">
-        <v>33.3</v>
+        <v>42.1</v>
       </c>
       <c r="H50">
-        <v>19.078407224959</v>
+        <v>27.2926929392447</v>
       </c>
       <c r="I50">
-        <v>16.7921686746988</v>
+        <v>25.933734939759</v>
       </c>
       <c r="J50">
-        <v>13.4075670498084</v>
+        <v>21.885775862069</v>
       </c>
       <c r="K50" t="s">
         <v>12</v>
@@ -3115,34 +3168,34 @@
     </row>
     <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B51" t="s">
-        <v>67</v>
-      </c>
-      <c r="C51">
-        <v>64</v>
-      </c>
-      <c r="D51">
-        <v>26.3</v>
-      </c>
-      <c r="E51">
-        <v>26.9839857651246</v>
-      </c>
-      <c r="F51">
-        <v>25.9995183044316</v>
-      </c>
-      <c r="G51">
-        <v>44.9</v>
-      </c>
-      <c r="H51">
-        <v>31.9622331691297</v>
-      </c>
-      <c r="I51">
-        <v>27.481593038822</v>
-      </c>
-      <c r="J51">
-        <v>22.2557471264368</v>
+        <v>12</v>
+      </c>
+      <c r="C51" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" t="s">
+        <v>12</v>
+      </c>
+      <c r="E51" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" t="s">
+        <v>12</v>
+      </c>
+      <c r="G51" t="s">
+        <v>12</v>
+      </c>
+      <c r="H51" t="s">
+        <v>12</v>
+      </c>
+      <c r="I51" t="s">
+        <v>12</v>
+      </c>
+      <c r="J51" t="s">
+        <v>12</v>
       </c>
       <c r="K51" t="s">
         <v>12</v>
@@ -3150,34 +3203,34 @@
     </row>
     <row r="52" spans="1:11">
       <c r="A52" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B52" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C52">
         <v>64</v>
       </c>
       <c r="D52">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="E52">
-        <v>9.91844602609727</v>
+        <v>9.67674970344009</v>
       </c>
       <c r="F52">
-        <v>12.6565510597302</v>
+        <v>12.5842967244701</v>
       </c>
       <c r="G52">
-        <v>27.3</v>
+        <v>26.2</v>
       </c>
       <c r="H52">
-        <v>16.3875205254516</v>
+        <v>14.9794745484401</v>
       </c>
       <c r="I52">
-        <v>10.6107764390897</v>
+        <v>11.303547523427</v>
       </c>
       <c r="J52">
-        <v>9.73299808429119</v>
+        <v>9.75574712643678</v>
       </c>
       <c r="K52" t="s">
         <v>12</v>
@@ -3185,34 +3238,34 @@
     </row>
     <row r="53" spans="1:11">
       <c r="A53" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B53" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C53">
         <v>64</v>
       </c>
       <c r="D53">
-        <v>15.7</v>
+        <v>18.2</v>
       </c>
       <c r="E53">
-        <v>17.1129893238434</v>
+        <v>18.573546856465</v>
       </c>
       <c r="F53">
-        <v>14.8843930635838</v>
+        <v>17.9431599229287</v>
       </c>
       <c r="G53">
-        <v>32.4</v>
+        <v>35.3</v>
       </c>
       <c r="H53">
-        <v>21.8226600985222</v>
+        <v>23.2676518883415</v>
       </c>
       <c r="I53">
-        <v>14.0110441767068</v>
+        <v>16.5779785809906</v>
       </c>
       <c r="J53">
-        <v>13.2614942528736</v>
+        <v>16.3230363984674</v>
       </c>
       <c r="K53" t="s">
         <v>12</v>
@@ -3220,34 +3273,34 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B54" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C54">
         <v>64</v>
       </c>
       <c r="D54">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="E54">
-        <v>10.7695729537367</v>
+        <v>10.0177935943061</v>
       </c>
       <c r="F54">
-        <v>12.4518304431599</v>
+        <v>12.7288053949904</v>
       </c>
       <c r="G54">
         <v>27</v>
       </c>
       <c r="H54">
-        <v>16.0940065681445</v>
+        <v>13.1055008210181</v>
       </c>
       <c r="I54">
-        <v>12.4732262382865</v>
+        <v>11.8457161981258</v>
       </c>
       <c r="J54">
-        <v>8.95354406130268</v>
+        <v>10.9518678160919</v>
       </c>
       <c r="K54" t="s">
         <v>12</v>
@@ -3255,34 +3308,34 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B55" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C55">
-        <v>64</v>
+        <v>512</v>
       </c>
       <c r="D55">
-        <v>19.4</v>
+        <v>14.4</v>
       </c>
       <c r="E55">
-        <v>20.3232502965599</v>
+        <v>13.0100830367734</v>
       </c>
       <c r="F55">
-        <v>18.9065510597303</v>
+        <v>15.0770712909441</v>
       </c>
       <c r="G55">
-        <v>36</v>
+        <v>29.7</v>
       </c>
       <c r="H55">
-        <v>24.9281609195402</v>
+        <v>16.9724958949097</v>
       </c>
       <c r="I55">
-        <v>18.7650602409639</v>
+        <v>16.7419678714859</v>
       </c>
       <c r="J55">
-        <v>16.6391283524904</v>
+        <v>11.1111111111111</v>
       </c>
       <c r="K55" t="s">
         <v>12</v>
@@ -3290,34 +3343,34 @@
     </row>
     <row r="56" spans="1:11">
       <c r="A56" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B56" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C56">
         <v>64</v>
       </c>
       <c r="D56">
-        <v>9.4</v>
+        <v>19.7</v>
       </c>
       <c r="E56">
-        <v>7.25237247924081</v>
+        <v>20.5026690391459</v>
       </c>
       <c r="F56">
-        <v>10.621387283237</v>
+        <v>19.1835260115607</v>
       </c>
       <c r="G56">
-        <v>23.7</v>
+        <v>37.2</v>
       </c>
       <c r="H56">
-        <v>14.072249589491</v>
+        <v>23.8711001642036</v>
       </c>
       <c r="I56">
-        <v>7.50502008032128</v>
+        <v>19.243641231593</v>
       </c>
       <c r="J56">
-        <v>8.11781609195402</v>
+        <v>17.4712643678161</v>
       </c>
       <c r="K56" t="s">
         <v>12</v>
@@ -3325,34 +3378,34 @@
     </row>
     <row r="57" spans="1:11">
       <c r="A57" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B57" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C57">
-        <v>64</v>
+        <v>512</v>
       </c>
       <c r="D57">
-        <v>14</v>
+        <v>20.2</v>
       </c>
       <c r="E57">
-        <v>14.4009489916963</v>
+        <v>20.2580071174377</v>
       </c>
       <c r="F57">
-        <v>13.764450867052</v>
+        <v>20.1107899807322</v>
       </c>
       <c r="G57">
-        <v>30.3</v>
+        <v>37.3</v>
       </c>
       <c r="H57">
-        <v>18.7889983579639</v>
+        <v>23.4626436781609</v>
       </c>
       <c r="I57">
-        <v>13.1726907630522</v>
+        <v>21.3570950468541</v>
       </c>
       <c r="J57">
-        <v>11.7708333333333</v>
+        <v>17.382662835249</v>
       </c>
       <c r="K57" t="s">
         <v>12</v>
@@ -3360,34 +3413,34 @@
     </row>
     <row r="58" spans="1:11">
       <c r="A58" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B58" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C58">
         <v>64</v>
       </c>
       <c r="D58">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="E58">
-        <v>10.6331553973903</v>
+        <v>12.4688612099644</v>
       </c>
       <c r="F58">
-        <v>14.7278420038536</v>
+        <v>14.1016377649326</v>
       </c>
       <c r="G58">
-        <v>29.6</v>
+        <v>29.4</v>
       </c>
       <c r="H58">
-        <v>14.8624794745484</v>
+        <v>17.4343185550082</v>
       </c>
       <c r="I58">
-        <v>14.6703480589023</v>
+        <v>13.7198795180723</v>
       </c>
       <c r="J58">
-        <v>11.3840996168582</v>
+        <v>11.1123084291188</v>
       </c>
       <c r="K58" t="s">
         <v>12</v>
@@ -3395,34 +3448,34 @@
     </row>
     <row r="59" spans="1:11">
       <c r="A59" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B59" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C59">
-        <v>64</v>
+        <v>512</v>
       </c>
       <c r="D59">
-        <v>21.8</v>
+        <v>13.2</v>
       </c>
       <c r="E59">
-        <v>24.288256227758</v>
+        <v>10.3766310794781</v>
       </c>
       <c r="F59">
-        <v>20.5202312138728</v>
+        <v>14.7639691714836</v>
       </c>
       <c r="G59">
-        <v>39.2</v>
+        <v>29.5</v>
       </c>
       <c r="H59">
-        <v>26.1761083743842</v>
+        <v>16.9396551724138</v>
       </c>
       <c r="I59">
-        <v>21.7453145917001</v>
+        <v>14.665327978581</v>
       </c>
       <c r="J59">
-        <v>19.3869731800766</v>
+        <v>10.0227490421456</v>
       </c>
       <c r="K59" t="s">
         <v>12</v>
@@ -3430,34 +3483,34 @@
     </row>
     <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B60" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C60">
         <v>64</v>
       </c>
       <c r="D60">
-        <v>12.7</v>
+        <v>21.1</v>
       </c>
       <c r="E60">
-        <v>10.3024911032029</v>
+        <v>22.5963819691578</v>
       </c>
       <c r="F60">
-        <v>13.9812138728324</v>
+        <v>20.2191714836224</v>
       </c>
       <c r="G60">
-        <v>27.7</v>
+        <v>38.6</v>
       </c>
       <c r="H60">
-        <v>17.3399014778325</v>
+        <v>26.9704433497537</v>
       </c>
       <c r="I60">
-        <v>13.3902275769746</v>
+        <v>21.0993975903614</v>
       </c>
       <c r="J60">
-        <v>9.47437739463602</v>
+        <v>17.5706417624521</v>
       </c>
       <c r="K60" t="s">
         <v>12</v>
@@ -3465,36 +3518,1436 @@
     </row>
     <row r="61" spans="1:11">
       <c r="A61" t="s">
+        <v>81</v>
+      </c>
+      <c r="B61" t="s">
+        <v>80</v>
+      </c>
+      <c r="C61">
+        <v>512</v>
+      </c>
+      <c r="D61">
+        <v>22.1</v>
+      </c>
+      <c r="E61">
+        <v>22.8039739027284</v>
+      </c>
+      <c r="F61">
+        <v>21.7003853564547</v>
+      </c>
+      <c r="G61">
+        <v>39.8</v>
+      </c>
+      <c r="H61">
+        <v>27.6190476190476</v>
+      </c>
+      <c r="I61">
+        <v>22.3845381526104</v>
+      </c>
+      <c r="J61">
+        <v>18.6494252873563</v>
+      </c>
+      <c r="K61" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" t="s">
+        <v>82</v>
+      </c>
+      <c r="B62" t="s">
+        <v>83</v>
+      </c>
+      <c r="C62">
+        <v>64</v>
+      </c>
+      <c r="D62">
+        <v>17.7</v>
+      </c>
+      <c r="E62">
+        <v>18.4193357058126</v>
+      </c>
+      <c r="F62">
+        <v>17.2447013487476</v>
+      </c>
+      <c r="G62">
+        <v>35.8</v>
+      </c>
+      <c r="H62">
+        <v>23.5550082101806</v>
+      </c>
+      <c r="I62">
+        <v>15.4852744310576</v>
+      </c>
+      <c r="J62">
+        <v>15.7710727969349</v>
+      </c>
+      <c r="K62" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" t="s">
+        <v>84</v>
+      </c>
+      <c r="B63" t="s">
+        <v>80</v>
+      </c>
+      <c r="C63">
+        <v>64</v>
+      </c>
+      <c r="D63">
+        <v>12.6</v>
+      </c>
+      <c r="E63">
+        <v>11.3804863582444</v>
+      </c>
+      <c r="F63">
+        <v>13.3068400770713</v>
+      </c>
+      <c r="G63">
+        <v>28.6</v>
+      </c>
+      <c r="H63">
+        <v>15.7984400656815</v>
+      </c>
+      <c r="I63">
+        <v>12.2740963855422</v>
+      </c>
+      <c r="J63">
+        <v>11.036877394636</v>
+      </c>
+      <c r="K63" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" t="s">
+        <v>85</v>
+      </c>
+      <c r="B64" t="s">
+        <v>83</v>
+      </c>
+      <c r="C64">
+        <v>64</v>
+      </c>
+      <c r="D64">
+        <v>19.5</v>
+      </c>
+      <c r="E64">
+        <v>21.2396204033215</v>
+      </c>
+      <c r="F64">
+        <v>18.5934489402697</v>
+      </c>
+      <c r="G64">
+        <v>36.5</v>
+      </c>
+      <c r="H64">
+        <v>24.7229064039409</v>
+      </c>
+      <c r="I64">
+        <v>17.4866131191432</v>
+      </c>
+      <c r="J64">
+        <v>17.9465996168582</v>
+      </c>
+      <c r="K64" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" t="s">
+        <v>86</v>
+      </c>
+      <c r="B65" t="s">
+        <v>80</v>
+      </c>
+      <c r="C65">
+        <v>64</v>
+      </c>
+      <c r="D65">
+        <v>18.3</v>
+      </c>
+      <c r="E65">
+        <v>20.4314946619217</v>
+      </c>
+      <c r="F65">
+        <v>17.1242774566474</v>
+      </c>
+      <c r="G65">
+        <v>36</v>
+      </c>
+      <c r="H65">
+        <v>23.3025451559934</v>
+      </c>
+      <c r="I65">
+        <v>15.826639892905</v>
+      </c>
+      <c r="J65">
+        <v>17.1192528735632</v>
+      </c>
+      <c r="K65" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" t="s">
+        <v>87</v>
+      </c>
+      <c r="B66" t="s">
+        <v>80</v>
+      </c>
+      <c r="C66">
+        <v>64</v>
+      </c>
+      <c r="D66">
+        <v>15.9</v>
+      </c>
+      <c r="E66">
+        <v>13.4386120996441</v>
+      </c>
+      <c r="F66">
+        <v>17.2326589595376</v>
+      </c>
+      <c r="G66">
+        <v>33.3</v>
+      </c>
+      <c r="H66">
+        <v>19.078407224959</v>
+      </c>
+      <c r="I66">
+        <v>16.7921686746988</v>
+      </c>
+      <c r="J66">
+        <v>13.4075670498084</v>
+      </c>
+      <c r="K66" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67" t="s">
+        <v>87</v>
+      </c>
+      <c r="B67" t="s">
+        <v>80</v>
+      </c>
+      <c r="C67">
+        <v>512</v>
+      </c>
+      <c r="D67">
+        <v>19</v>
+      </c>
+      <c r="E67">
+        <v>16.4679715302491</v>
+      </c>
+      <c r="F67">
+        <v>20.3757225433526</v>
+      </c>
+      <c r="G67">
+        <v>36.8</v>
+      </c>
+      <c r="H67">
+        <v>21.3608374384236</v>
+      </c>
+      <c r="I67">
+        <v>23.3885542168675</v>
+      </c>
+      <c r="J67">
+        <v>14.4899425287356</v>
+      </c>
+      <c r="K67" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68" t="s">
+        <v>88</v>
+      </c>
+      <c r="B68" t="s">
+        <v>80</v>
+      </c>
+      <c r="C68">
+        <v>64</v>
+      </c>
+      <c r="D68">
+        <v>26.3</v>
+      </c>
+      <c r="E68">
+        <v>26.9839857651246</v>
+      </c>
+      <c r="F68">
+        <v>25.9995183044316</v>
+      </c>
+      <c r="G68">
+        <v>44.9</v>
+      </c>
+      <c r="H68">
+        <v>31.9622331691297</v>
+      </c>
+      <c r="I68">
+        <v>27.481593038822</v>
+      </c>
+      <c r="J68">
+        <v>22.2557471264368</v>
+      </c>
+      <c r="K68" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" t="s">
+        <v>88</v>
+      </c>
+      <c r="B69" t="s">
+        <v>80</v>
+      </c>
+      <c r="C69">
+        <v>512</v>
+      </c>
+      <c r="D69">
+        <v>28.1</v>
+      </c>
+      <c r="E69">
+        <v>27.7669039145907</v>
+      </c>
+      <c r="F69">
+        <v>28.2755298651252</v>
+      </c>
+      <c r="G69">
+        <v>47.2</v>
+      </c>
+      <c r="H69">
+        <v>32.5964696223317</v>
+      </c>
+      <c r="I69">
+        <v>30.3229585006693</v>
+      </c>
+      <c r="J69">
+        <v>23.8793103448276</v>
+      </c>
+      <c r="K69" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" t="s">
+        <v>89</v>
+      </c>
+      <c r="B70" t="s">
         <v>90</v>
       </c>
-      <c r="B61" t="s">
-        <v>89</v>
-      </c>
-      <c r="C61">
-        <v>64</v>
-      </c>
-      <c r="D61">
+      <c r="C70">
+        <v>64</v>
+      </c>
+      <c r="D70">
+        <v>11.7</v>
+      </c>
+      <c r="E70">
+        <v>9.91844602609727</v>
+      </c>
+      <c r="F70">
+        <v>12.6565510597302</v>
+      </c>
+      <c r="G70">
+        <v>27.3</v>
+      </c>
+      <c r="H70">
+        <v>16.3875205254516</v>
+      </c>
+      <c r="I70">
+        <v>10.6107764390897</v>
+      </c>
+      <c r="J70">
+        <v>9.73299808429119</v>
+      </c>
+      <c r="K70" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" t="s">
+        <v>91</v>
+      </c>
+      <c r="B71" t="s">
+        <v>90</v>
+      </c>
+      <c r="C71">
+        <v>64</v>
+      </c>
+      <c r="D71">
+        <v>15.7</v>
+      </c>
+      <c r="E71">
+        <v>17.1129893238434</v>
+      </c>
+      <c r="F71">
+        <v>14.8843930635838</v>
+      </c>
+      <c r="G71">
+        <v>32.4</v>
+      </c>
+      <c r="H71">
+        <v>21.8226600985222</v>
+      </c>
+      <c r="I71">
+        <v>14.0110441767068</v>
+      </c>
+      <c r="J71">
+        <v>13.2614942528736</v>
+      </c>
+      <c r="K71" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" t="s">
+        <v>92</v>
+      </c>
+      <c r="B72" t="s">
+        <v>93</v>
+      </c>
+      <c r="C72">
+        <v>64</v>
+      </c>
+      <c r="D72">
+        <v>11.9</v>
+      </c>
+      <c r="E72">
+        <v>10.7695729537367</v>
+      </c>
+      <c r="F72">
+        <v>12.4518304431599</v>
+      </c>
+      <c r="G72">
+        <v>27</v>
+      </c>
+      <c r="H72">
+        <v>16.0940065681445</v>
+      </c>
+      <c r="I72">
+        <v>12.4732262382865</v>
+      </c>
+      <c r="J72">
+        <v>8.95354406130268</v>
+      </c>
+      <c r="K72" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" t="s">
+        <v>94</v>
+      </c>
+      <c r="B73" t="s">
+        <v>93</v>
+      </c>
+      <c r="C73">
+        <v>64</v>
+      </c>
+      <c r="D73">
+        <v>19.4</v>
+      </c>
+      <c r="E73">
+        <v>20.3232502965599</v>
+      </c>
+      <c r="F73">
+        <v>18.9065510597303</v>
+      </c>
+      <c r="G73">
+        <v>36</v>
+      </c>
+      <c r="H73">
+        <v>24.9281609195402</v>
+      </c>
+      <c r="I73">
+        <v>18.7650602409639</v>
+      </c>
+      <c r="J73">
+        <v>16.6391283524904</v>
+      </c>
+      <c r="K73" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" t="s">
+        <v>95</v>
+      </c>
+      <c r="B74" t="s">
+        <v>96</v>
+      </c>
+      <c r="C74">
+        <v>64</v>
+      </c>
+      <c r="D74">
+        <v>9.4</v>
+      </c>
+      <c r="E74">
+        <v>7.25237247924081</v>
+      </c>
+      <c r="F74">
+        <v>10.621387283237</v>
+      </c>
+      <c r="G74">
+        <v>23.7</v>
+      </c>
+      <c r="H74">
+        <v>14.072249589491</v>
+      </c>
+      <c r="I74">
+        <v>7.50502008032128</v>
+      </c>
+      <c r="J74">
+        <v>8.11781609195402</v>
+      </c>
+      <c r="K74" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75" t="s">
+        <v>97</v>
+      </c>
+      <c r="B75" t="s">
+        <v>96</v>
+      </c>
+      <c r="C75">
+        <v>64</v>
+      </c>
+      <c r="D75">
+        <v>14</v>
+      </c>
+      <c r="E75">
+        <v>14.4009489916963</v>
+      </c>
+      <c r="F75">
+        <v>13.764450867052</v>
+      </c>
+      <c r="G75">
+        <v>30.3</v>
+      </c>
+      <c r="H75">
+        <v>18.7889983579639</v>
+      </c>
+      <c r="I75">
+        <v>13.1726907630522</v>
+      </c>
+      <c r="J75">
+        <v>11.7708333333333</v>
+      </c>
+      <c r="K75" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76" t="s">
+        <v>98</v>
+      </c>
+      <c r="B76" t="s">
+        <v>99</v>
+      </c>
+      <c r="C76">
+        <v>64</v>
+      </c>
+      <c r="D76">
+        <v>13.3</v>
+      </c>
+      <c r="E76">
+        <v>10.6331553973903</v>
+      </c>
+      <c r="F76">
+        <v>14.7278420038536</v>
+      </c>
+      <c r="G76">
+        <v>29.6</v>
+      </c>
+      <c r="H76">
+        <v>14.8624794745484</v>
+      </c>
+      <c r="I76">
+        <v>14.6703480589023</v>
+      </c>
+      <c r="J76">
+        <v>11.3840996168582</v>
+      </c>
+      <c r="K76" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77" t="s">
+        <v>100</v>
+      </c>
+      <c r="B77" t="s">
+        <v>99</v>
+      </c>
+      <c r="C77">
+        <v>64</v>
+      </c>
+      <c r="D77">
+        <v>21.8</v>
+      </c>
+      <c r="E77">
+        <v>24.288256227758</v>
+      </c>
+      <c r="F77">
+        <v>20.5202312138728</v>
+      </c>
+      <c r="G77">
+        <v>39.2</v>
+      </c>
+      <c r="H77">
+        <v>26.1761083743842</v>
+      </c>
+      <c r="I77">
+        <v>21.7453145917001</v>
+      </c>
+      <c r="J77">
+        <v>19.3869731800766</v>
+      </c>
+      <c r="K77" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" t="s">
+        <v>101</v>
+      </c>
+      <c r="B78" t="s">
+        <v>102</v>
+      </c>
+      <c r="C78">
+        <v>64</v>
+      </c>
+      <c r="D78">
+        <v>12.7</v>
+      </c>
+      <c r="E78">
+        <v>10.3024911032029</v>
+      </c>
+      <c r="F78">
+        <v>13.9812138728324</v>
+      </c>
+      <c r="G78">
+        <v>27.7</v>
+      </c>
+      <c r="H78">
+        <v>17.3399014778325</v>
+      </c>
+      <c r="I78">
+        <v>13.3902275769746</v>
+      </c>
+      <c r="J78">
+        <v>9.47437739463602</v>
+      </c>
+      <c r="K78" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79" t="s">
+        <v>103</v>
+      </c>
+      <c r="B79" t="s">
+        <v>102</v>
+      </c>
+      <c r="C79">
+        <v>64</v>
+      </c>
+      <c r="D79">
         <v>19.8</v>
       </c>
-      <c r="E61">
+      <c r="E79">
         <v>19.9614472123369</v>
       </c>
-      <c r="F61">
+      <c r="F79">
         <v>19.6411368015414</v>
       </c>
-      <c r="G61">
+      <c r="G79">
         <v>37.4</v>
       </c>
-      <c r="H61">
+      <c r="H79">
         <v>26.7857142857143</v>
       </c>
-      <c r="I61">
+      <c r="I79">
         <v>19.3875502008032</v>
       </c>
-      <c r="J61">
+      <c r="J79">
         <v>15.9135536398467</v>
       </c>
-      <c r="K61" t="s">
+      <c r="K79" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80" t="s">
+        <v>104</v>
+      </c>
+      <c r="B80" t="s">
+        <v>105</v>
+      </c>
+      <c r="C80">
+        <v>64</v>
+      </c>
+      <c r="D80">
+        <v>11.6</v>
+      </c>
+      <c r="E80">
+        <v>10.0296559905101</v>
+      </c>
+      <c r="F80">
+        <v>12.3795761078998</v>
+      </c>
+      <c r="G80">
+        <v>26.5</v>
+      </c>
+      <c r="H80">
+        <v>14.9035303776683</v>
+      </c>
+      <c r="I80">
+        <v>11.1010709504685</v>
+      </c>
+      <c r="J80">
+        <v>9.92456896551724</v>
+      </c>
+      <c r="K80" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81" t="s">
+        <v>62</v>
+      </c>
+      <c r="B81" t="s">
+        <v>105</v>
+      </c>
+      <c r="C81">
+        <v>64</v>
+      </c>
+      <c r="D81">
+        <v>20.7</v>
+      </c>
+      <c r="E81">
+        <v>21.3967971530249</v>
+      </c>
+      <c r="F81">
+        <v>20.3516377649326</v>
+      </c>
+      <c r="G81">
+        <v>38.8</v>
+      </c>
+      <c r="H81">
+        <v>26.2335796387521</v>
+      </c>
+      <c r="I81">
+        <v>21.0240963855422</v>
+      </c>
+      <c r="J81">
+        <v>17.283285440613</v>
+      </c>
+      <c r="K81" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82" t="s">
+        <v>63</v>
+      </c>
+      <c r="B82" t="s">
+        <v>105</v>
+      </c>
+      <c r="C82">
+        <v>64</v>
+      </c>
+      <c r="D82">
+        <v>13.7</v>
+      </c>
+      <c r="E82">
+        <v>13.1242586002372</v>
+      </c>
+      <c r="F82">
+        <v>13.9450867052023</v>
+      </c>
+      <c r="G82">
+        <v>28.9</v>
+      </c>
+      <c r="H82">
+        <v>16.6974548440066</v>
+      </c>
+      <c r="I82">
+        <v>12.6305220883534</v>
+      </c>
+      <c r="J82">
+        <v>12.617337164751</v>
+      </c>
+      <c r="K82" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83" t="s">
+        <v>63</v>
+      </c>
+      <c r="B83" t="s">
+        <v>105</v>
+      </c>
+      <c r="C83">
+        <v>512</v>
+      </c>
+      <c r="D83">
+        <v>19.5</v>
+      </c>
+      <c r="E83">
+        <v>16.8431198102017</v>
+      </c>
+      <c r="F83">
+        <v>20.9898843930636</v>
+      </c>
+      <c r="G83">
+        <v>36.8</v>
+      </c>
+      <c r="H83">
+        <v>21.8390804597701</v>
+      </c>
+      <c r="I83">
+        <v>24.489625167336</v>
+      </c>
+      <c r="J83">
+        <v>14.6420019157088</v>
+      </c>
+      <c r="K83" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84" t="s">
+        <v>64</v>
+      </c>
+      <c r="B84" t="s">
+        <v>105</v>
+      </c>
+      <c r="C84">
+        <v>64</v>
+      </c>
+      <c r="D84">
+        <v>23.2</v>
+      </c>
+      <c r="E84">
+        <v>22.2479240806643</v>
+      </c>
+      <c r="F84">
+        <v>23.6392100192678</v>
+      </c>
+      <c r="G84">
+        <v>40.3</v>
+      </c>
+      <c r="H84">
+        <v>28.2635467980296</v>
+      </c>
+      <c r="I84">
+        <v>24.7322623828648</v>
+      </c>
+      <c r="J84">
+        <v>19.0361590038314</v>
+      </c>
+      <c r="K84" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85" t="s">
+        <v>64</v>
+      </c>
+      <c r="B85" t="s">
+        <v>105</v>
+      </c>
+      <c r="C85">
+        <v>512</v>
+      </c>
+      <c r="D85">
+        <v>26.2</v>
+      </c>
+      <c r="E85">
+        <v>26.8030842230131</v>
+      </c>
+      <c r="F85">
+        <v>25.8429672447013</v>
+      </c>
+      <c r="G85">
+        <v>44.5</v>
+      </c>
+      <c r="H85">
+        <v>30.4741379310345</v>
+      </c>
+      <c r="I85">
+        <v>30.1188085676038</v>
+      </c>
+      <c r="J85">
+        <v>20.8572796934866</v>
+      </c>
+      <c r="K85" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" t="s">
+        <v>65</v>
+      </c>
+      <c r="B86" t="s">
+        <v>105</v>
+      </c>
+      <c r="C86">
+        <v>64</v>
+      </c>
+      <c r="D86">
+        <v>17.6</v>
+      </c>
+      <c r="E86">
+        <v>16.4249703440095</v>
+      </c>
+      <c r="F86">
+        <v>18.1840077071291</v>
+      </c>
+      <c r="G86">
+        <v>34.5</v>
+      </c>
+      <c r="H86">
+        <v>19.9815270935961</v>
+      </c>
+      <c r="I86">
+        <v>18.5056894243641</v>
+      </c>
+      <c r="J86">
+        <v>15.4849137931035</v>
+      </c>
+      <c r="K86" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87" t="s">
+        <v>65</v>
+      </c>
+      <c r="B87" t="s">
+        <v>105</v>
+      </c>
+      <c r="C87">
+        <v>512</v>
+      </c>
+      <c r="D87">
+        <v>19.5</v>
+      </c>
+      <c r="E87">
+        <v>16.4739027283511</v>
+      </c>
+      <c r="F87">
+        <v>20.5924855491329</v>
+      </c>
+      <c r="G87">
+        <v>37.4</v>
+      </c>
+      <c r="H87">
+        <v>22.3173234811166</v>
+      </c>
+      <c r="I87">
+        <v>23.1492637215529</v>
+      </c>
+      <c r="J87">
+        <v>14.4312739463602</v>
+      </c>
+      <c r="K87" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88" t="s">
+        <v>66</v>
+      </c>
+      <c r="B88" t="s">
+        <v>105</v>
+      </c>
+      <c r="C88">
+        <v>64</v>
+      </c>
+      <c r="D88">
+        <v>29.6</v>
+      </c>
+      <c r="E88">
+        <v>31.6711150652432</v>
+      </c>
+      <c r="F88">
+        <v>28.5404624277457</v>
+      </c>
+      <c r="G88">
+        <v>47.6</v>
+      </c>
+      <c r="H88">
+        <v>34.997947454844</v>
+      </c>
+      <c r="I88">
+        <v>30.5856760374833</v>
+      </c>
+      <c r="J88">
+        <v>25.838122605364</v>
+      </c>
+      <c r="K88" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89" t="s">
+        <v>66</v>
+      </c>
+      <c r="B89" t="s">
+        <v>105</v>
+      </c>
+      <c r="C89">
+        <v>512</v>
+      </c>
+      <c r="D89">
+        <v>31.4</v>
+      </c>
+      <c r="E89">
+        <v>31.2574139976275</v>
+      </c>
+      <c r="F89">
+        <v>31.5149325626204</v>
+      </c>
+      <c r="G89">
+        <v>49.6</v>
+      </c>
+      <c r="H89">
+        <v>34.3534482758621</v>
+      </c>
+      <c r="I89">
+        <v>36.3922356091031</v>
+      </c>
+      <c r="J89">
+        <v>26.1613984674329</v>
+      </c>
+      <c r="K89" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90" t="s">
+        <v>67</v>
+      </c>
+      <c r="B90" t="s">
+        <v>105</v>
+      </c>
+      <c r="C90">
+        <v>64</v>
+      </c>
+      <c r="D90">
+        <v>15.6</v>
+      </c>
+      <c r="E90">
+        <v>14.629300118624</v>
+      </c>
+      <c r="F90">
+        <v>16.0765895953757</v>
+      </c>
+      <c r="G90">
+        <v>32.6</v>
+      </c>
+      <c r="H90">
+        <v>18.1547619047619</v>
+      </c>
+      <c r="I90">
+        <v>15.8467202141901</v>
+      </c>
+      <c r="J90">
+        <v>13.860153256705</v>
+      </c>
+      <c r="K90" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91" t="s">
+        <v>67</v>
+      </c>
+      <c r="B91" t="s">
+        <v>105</v>
+      </c>
+      <c r="C91">
+        <v>512</v>
+      </c>
+      <c r="D91">
+        <v>12.2</v>
+      </c>
+      <c r="E91">
+        <v>11.0513048635824</v>
+      </c>
+      <c r="F91">
+        <v>12.7890173410405</v>
+      </c>
+      <c r="G91">
+        <v>28.5</v>
+      </c>
+      <c r="H91">
+        <v>13.9326765188834</v>
+      </c>
+      <c r="I91">
+        <v>11.3922356091031</v>
+      </c>
+      <c r="J91">
+        <v>11.7181513409962</v>
+      </c>
+      <c r="K91" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92" t="s">
+        <v>68</v>
+      </c>
+      <c r="B92" t="s">
+        <v>105</v>
+      </c>
+      <c r="C92">
+        <v>64</v>
+      </c>
+      <c r="D92">
+        <v>25.8</v>
+      </c>
+      <c r="E92">
+        <v>27.5385527876631</v>
+      </c>
+      <c r="F92">
+        <v>24.8554913294798</v>
+      </c>
+      <c r="G92">
+        <v>43.9</v>
+      </c>
+      <c r="H92">
+        <v>31.2828407224959</v>
+      </c>
+      <c r="I92">
+        <v>24.894578313253</v>
+      </c>
+      <c r="J92">
+        <v>23.2447318007663</v>
+      </c>
+      <c r="K92" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93" t="s">
+        <v>68</v>
+      </c>
+      <c r="B93" t="s">
+        <v>105</v>
+      </c>
+      <c r="C93">
+        <v>512</v>
+      </c>
+      <c r="D93">
+        <v>23.9</v>
+      </c>
+      <c r="E93">
+        <v>24.6975088967971</v>
+      </c>
+      <c r="F93">
+        <v>23.3983622350674</v>
+      </c>
+      <c r="G93">
+        <v>41.5</v>
+      </c>
+      <c r="H93">
+        <v>29.5402298850575</v>
+      </c>
+      <c r="I93">
+        <v>24.4996653279786</v>
+      </c>
+      <c r="J93">
+        <v>20.0766283524904</v>
+      </c>
+      <c r="K93" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94" t="s">
+        <v>69</v>
+      </c>
+      <c r="B94" t="s">
+        <v>105</v>
+      </c>
+      <c r="C94">
+        <v>64</v>
+      </c>
+      <c r="D94">
+        <v>16.3</v>
+      </c>
+      <c r="E94">
+        <v>15.2698695136417</v>
+      </c>
+      <c r="F94">
+        <v>16.7991329479769</v>
+      </c>
+      <c r="G94">
+        <v>33</v>
+      </c>
+      <c r="H94">
+        <v>18.9573070607553</v>
+      </c>
+      <c r="I94">
+        <v>15.9906291834003</v>
+      </c>
+      <c r="J94">
+        <v>14.8838601532567</v>
+      </c>
+      <c r="K94" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" t="s">
+        <v>69</v>
+      </c>
+      <c r="B95" t="s">
+        <v>105</v>
+      </c>
+      <c r="C95">
+        <v>512</v>
+      </c>
+      <c r="D95">
+        <v>14</v>
+      </c>
+      <c r="E95">
+        <v>12.8959074733096</v>
+      </c>
+      <c r="F95">
+        <v>14.5472061657033</v>
+      </c>
+      <c r="G95">
+        <v>30.6</v>
+      </c>
+      <c r="H95">
+        <v>15.7717569786535</v>
+      </c>
+      <c r="I95">
+        <v>13.9574966532798</v>
+      </c>
+      <c r="J95">
+        <v>12.9214559386973</v>
+      </c>
+      <c r="K95" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11">
+      <c r="A96" t="s">
+        <v>70</v>
+      </c>
+      <c r="B96" t="s">
+        <v>105</v>
+      </c>
+      <c r="C96">
+        <v>64</v>
+      </c>
+      <c r="D96">
+        <v>26.7</v>
+      </c>
+      <c r="E96">
+        <v>27.2553380782918</v>
+      </c>
+      <c r="F96">
+        <v>26.4210019267823</v>
+      </c>
+      <c r="G96">
+        <v>45.1</v>
+      </c>
+      <c r="H96">
+        <v>30.1128899835796</v>
+      </c>
+      <c r="I96">
+        <v>27.8815261044177</v>
+      </c>
+      <c r="J96">
+        <v>23.8960727969349</v>
+      </c>
+      <c r="K96" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11">
+      <c r="A97" t="s">
+        <v>70</v>
+      </c>
+      <c r="B97" t="s">
+        <v>105</v>
+      </c>
+      <c r="C97">
+        <v>512</v>
+      </c>
+      <c r="D97">
+        <v>25.1</v>
+      </c>
+      <c r="E97">
+        <v>26.4798339264531</v>
+      </c>
+      <c r="F97">
+        <v>24.3376685934489</v>
+      </c>
+      <c r="G97">
+        <v>43.4</v>
+      </c>
+      <c r="H97">
+        <v>27.4466338259442</v>
+      </c>
+      <c r="I97">
+        <v>25.563922356091</v>
+      </c>
+      <c r="J97">
+        <v>23.3764367816092</v>
+      </c>
+      <c r="K97" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11">
+      <c r="A98" t="s">
+        <v>71</v>
+      </c>
+      <c r="B98" t="s">
+        <v>105</v>
+      </c>
+      <c r="C98">
+        <v>64</v>
+      </c>
+      <c r="D98" t="s">
+        <v>12</v>
+      </c>
+      <c r="E98" t="s">
+        <v>12</v>
+      </c>
+      <c r="F98" t="s">
+        <v>12</v>
+      </c>
+      <c r="G98" t="s">
+        <v>12</v>
+      </c>
+      <c r="H98" t="s">
+        <v>12</v>
+      </c>
+      <c r="I98" t="s">
+        <v>12</v>
+      </c>
+      <c r="J98" t="s">
+        <v>12</v>
+      </c>
+      <c r="K98" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99" t="s">
+        <v>71</v>
+      </c>
+      <c r="B99" t="s">
+        <v>105</v>
+      </c>
+      <c r="C99">
+        <v>512</v>
+      </c>
+      <c r="D99" t="s">
+        <v>12</v>
+      </c>
+      <c r="E99" t="s">
+        <v>12</v>
+      </c>
+      <c r="F99" t="s">
+        <v>12</v>
+      </c>
+      <c r="G99" t="s">
+        <v>12</v>
+      </c>
+      <c r="H99" t="s">
+        <v>12</v>
+      </c>
+      <c r="I99" t="s">
+        <v>12</v>
+      </c>
+      <c r="J99" t="s">
+        <v>12</v>
+      </c>
+      <c r="K99" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100" t="s">
+        <v>72</v>
+      </c>
+      <c r="B100" t="s">
+        <v>105</v>
+      </c>
+      <c r="C100">
+        <v>64</v>
+      </c>
+      <c r="D100" t="s">
+        <v>12</v>
+      </c>
+      <c r="E100" t="s">
+        <v>12</v>
+      </c>
+      <c r="F100" t="s">
+        <v>12</v>
+      </c>
+      <c r="G100" t="s">
+        <v>12</v>
+      </c>
+      <c r="H100" t="s">
+        <v>12</v>
+      </c>
+      <c r="I100" t="s">
+        <v>12</v>
+      </c>
+      <c r="J100" t="s">
+        <v>12</v>
+      </c>
+      <c r="K100" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101" t="s">
+        <v>72</v>
+      </c>
+      <c r="B101" t="s">
+        <v>105</v>
+      </c>
+      <c r="C101">
+        <v>512</v>
+      </c>
+      <c r="D101" t="s">
+        <v>12</v>
+      </c>
+      <c r="E101" t="s">
+        <v>12</v>
+      </c>
+      <c r="F101" t="s">
+        <v>12</v>
+      </c>
+      <c r="G101" t="s">
+        <v>12</v>
+      </c>
+      <c r="H101" t="s">
+        <v>12</v>
+      </c>
+      <c r="I101" t="s">
+        <v>12</v>
+      </c>
+      <c r="J101" t="s">
+        <v>12</v>
+      </c>
+      <c r="K101" t="s">
         <v>12</v>
       </c>
     </row>

--- a/figs/exps/performance_parsed.xlsx
+++ b/figs/exps/performance_parsed.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="107">
   <si>
     <t>模型</t>
   </si>
@@ -244,7 +244,7 @@
     <t>Keye-VL-1_5-8B-sub</t>
   </si>
   <si>
-    <t>Qwen3.5-4B-Instruct</t>
+    <t>Qwen3.5-4B</t>
   </si>
   <si>
     <t>temperature=0.7, 
@@ -344,7 +344,13 @@
     <t>Qwen3-VL-235B-A22B-Think</t>
   </si>
   <si>
+    <t>Qwen3-VL-235B-A22B-Think-random</t>
+  </si>
+  <si>
     <t>Qwen3-VL-235B-A22B-Think-sub</t>
+  </si>
+  <si>
+    <t>Qwen3-VL-235B-A22B-Think-sub-interleave</t>
   </si>
   <si>
     <t>KimiVL-16B-A3B-Think</t>
@@ -407,9 +413,6 @@
   </si>
   <si>
     <t>GLM4.6-flash-sub</t>
-  </si>
-  <si>
-    <t>Qwen3.5-4B</t>
   </si>
   <si>
     <t>temperature=1.0,
@@ -1410,10 +1413,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="47.1057692307692" customWidth="1"/>
+    <col min="1" max="1" width="59.2980769230769" customWidth="1"/>
+    <col min="5" max="6" width="12.9230769230769"/>
+    <col min="8" max="10" width="12.9230769230769"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -3769,28 +3774,28 @@
         <v>80</v>
       </c>
       <c r="C68">
-        <v>64</v>
+        <v>512</v>
       </c>
       <c r="D68">
-        <v>26.3</v>
+        <v>12.9</v>
       </c>
       <c r="E68">
-        <v>26.9839857651246</v>
+        <v>12.1767497034401</v>
       </c>
       <c r="F68">
-        <v>25.9995183044316</v>
+        <v>13.3309248554913</v>
       </c>
       <c r="G68">
-        <v>44.9</v>
+        <v>29.3</v>
       </c>
       <c r="H68">
-        <v>31.9622331691297</v>
+        <v>16.5291461412151</v>
       </c>
       <c r="I68">
-        <v>27.481593038822</v>
+        <v>11.3755020080321</v>
       </c>
       <c r="J68">
-        <v>22.2557471264368</v>
+        <v>11.9324712643678</v>
       </c>
       <c r="K68" t="s">
         <v>12</v>
@@ -3798,34 +3803,34 @@
     </row>
     <row r="69" spans="1:11">
       <c r="A69" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B69" t="s">
         <v>80</v>
       </c>
       <c r="C69">
-        <v>512</v>
+        <v>64</v>
       </c>
       <c r="D69">
-        <v>28.1</v>
+        <v>26.3</v>
       </c>
       <c r="E69">
-        <v>27.7669039145907</v>
+        <v>26.9839857651246</v>
       </c>
       <c r="F69">
-        <v>28.2755298651252</v>
+        <v>25.9995183044316</v>
       </c>
       <c r="G69">
-        <v>47.2</v>
+        <v>44.9</v>
       </c>
       <c r="H69">
-        <v>32.5964696223317</v>
+        <v>31.9622331691297</v>
       </c>
       <c r="I69">
-        <v>30.3229585006693</v>
+        <v>27.481593038822</v>
       </c>
       <c r="J69">
-        <v>23.8793103448276</v>
+        <v>22.2557471264368</v>
       </c>
       <c r="K69" t="s">
         <v>12</v>
@@ -3836,31 +3841,31 @@
         <v>89</v>
       </c>
       <c r="B70" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C70">
-        <v>64</v>
+        <v>512</v>
       </c>
       <c r="D70">
-        <v>11.7</v>
+        <v>28.1</v>
       </c>
       <c r="E70">
-        <v>9.91844602609727</v>
+        <v>27.7669039145907</v>
       </c>
       <c r="F70">
-        <v>12.6565510597302</v>
+        <v>28.2755298651252</v>
       </c>
       <c r="G70">
-        <v>27.3</v>
+        <v>47.2</v>
       </c>
       <c r="H70">
-        <v>16.3875205254516</v>
+        <v>32.5964696223317</v>
       </c>
       <c r="I70">
-        <v>10.6107764390897</v>
+        <v>30.3229585006693</v>
       </c>
       <c r="J70">
-        <v>9.73299808429119</v>
+        <v>23.8793103448276</v>
       </c>
       <c r="K70" t="s">
         <v>12</v>
@@ -3868,34 +3873,34 @@
     </row>
     <row r="71" spans="1:11">
       <c r="A71" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B71" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C71">
-        <v>64</v>
+        <v>512</v>
       </c>
       <c r="D71">
-        <v>15.7</v>
+        <v>30.3</v>
       </c>
       <c r="E71">
-        <v>17.1129893238434</v>
+        <v>28.7292408066429</v>
       </c>
       <c r="F71">
-        <v>14.8843930635838</v>
+        <v>31.1054913294798</v>
       </c>
       <c r="G71">
-        <v>32.4</v>
+        <v>49</v>
       </c>
       <c r="H71">
-        <v>21.8226600985222</v>
+        <v>43.8177339901478</v>
       </c>
       <c r="I71">
-        <v>14.0110441767068</v>
+        <v>28.6462516733601</v>
       </c>
       <c r="J71">
-        <v>13.2614942528736</v>
+        <v>23.5308908045977</v>
       </c>
       <c r="K71" t="s">
         <v>12</v>
@@ -3903,34 +3908,34 @@
     </row>
     <row r="72" spans="1:11">
       <c r="A72" t="s">
+        <v>91</v>
+      </c>
+      <c r="B72" t="s">
         <v>92</v>
       </c>
-      <c r="B72" t="s">
-        <v>93</v>
-      </c>
       <c r="C72">
         <v>64</v>
       </c>
       <c r="D72">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="E72">
-        <v>10.7695729537367</v>
+        <v>9.91844602609727</v>
       </c>
       <c r="F72">
-        <v>12.4518304431599</v>
+        <v>12.6565510597302</v>
       </c>
       <c r="G72">
-        <v>27</v>
+        <v>27.3</v>
       </c>
       <c r="H72">
-        <v>16.0940065681445</v>
+        <v>16.3875205254516</v>
       </c>
       <c r="I72">
-        <v>12.4732262382865</v>
+        <v>10.6107764390897</v>
       </c>
       <c r="J72">
-        <v>8.95354406130268</v>
+        <v>9.73299808429119</v>
       </c>
       <c r="K72" t="s">
         <v>12</v>
@@ -3938,34 +3943,34 @@
     </row>
     <row r="73" spans="1:11">
       <c r="A73" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C73">
         <v>64</v>
       </c>
       <c r="D73">
-        <v>19.4</v>
+        <v>15.7</v>
       </c>
       <c r="E73">
-        <v>20.3232502965599</v>
+        <v>17.1129893238434</v>
       </c>
       <c r="F73">
-        <v>18.9065510597303</v>
+        <v>14.8843930635838</v>
       </c>
       <c r="G73">
-        <v>36</v>
+        <v>32.4</v>
       </c>
       <c r="H73">
-        <v>24.9281609195402</v>
+        <v>21.8226600985222</v>
       </c>
       <c r="I73">
-        <v>18.7650602409639</v>
+        <v>14.0110441767068</v>
       </c>
       <c r="J73">
-        <v>16.6391283524904</v>
+        <v>13.2614942528736</v>
       </c>
       <c r="K73" t="s">
         <v>12</v>
@@ -3973,34 +3978,34 @@
     </row>
     <row r="74" spans="1:11">
       <c r="A74" t="s">
+        <v>94</v>
+      </c>
+      <c r="B74" t="s">
         <v>95</v>
       </c>
-      <c r="B74" t="s">
-        <v>96</v>
-      </c>
       <c r="C74">
         <v>64</v>
       </c>
       <c r="D74">
-        <v>9.4</v>
+        <v>11.9</v>
       </c>
       <c r="E74">
-        <v>7.25237247924081</v>
+        <v>10.7695729537367</v>
       </c>
       <c r="F74">
-        <v>10.621387283237</v>
+        <v>12.4518304431599</v>
       </c>
       <c r="G74">
-        <v>23.7</v>
+        <v>27</v>
       </c>
       <c r="H74">
-        <v>14.072249589491</v>
+        <v>16.0940065681445</v>
       </c>
       <c r="I74">
-        <v>7.50502008032128</v>
+        <v>12.4732262382865</v>
       </c>
       <c r="J74">
-        <v>8.11781609195402</v>
+        <v>8.95354406130268</v>
       </c>
       <c r="K74" t="s">
         <v>12</v>
@@ -4008,34 +4013,34 @@
     </row>
     <row r="75" spans="1:11">
       <c r="A75" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B75" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C75">
         <v>64</v>
       </c>
       <c r="D75">
-        <v>14</v>
+        <v>19.4</v>
       </c>
       <c r="E75">
-        <v>14.4009489916963</v>
+        <v>20.3232502965599</v>
       </c>
       <c r="F75">
-        <v>13.764450867052</v>
+        <v>18.9065510597303</v>
       </c>
       <c r="G75">
-        <v>30.3</v>
+        <v>36</v>
       </c>
       <c r="H75">
-        <v>18.7889983579639</v>
+        <v>24.9281609195402</v>
       </c>
       <c r="I75">
-        <v>13.1726907630522</v>
+        <v>18.7650602409639</v>
       </c>
       <c r="J75">
-        <v>11.7708333333333</v>
+        <v>16.6391283524904</v>
       </c>
       <c r="K75" t="s">
         <v>12</v>
@@ -4043,34 +4048,34 @@
     </row>
     <row r="76" spans="1:11">
       <c r="A76" t="s">
+        <v>97</v>
+      </c>
+      <c r="B76" t="s">
         <v>98</v>
       </c>
-      <c r="B76" t="s">
-        <v>99</v>
-      </c>
       <c r="C76">
         <v>64</v>
       </c>
       <c r="D76">
-        <v>13.3</v>
+        <v>9.4</v>
       </c>
       <c r="E76">
-        <v>10.6331553973903</v>
+        <v>7.25237247924081</v>
       </c>
       <c r="F76">
-        <v>14.7278420038536</v>
+        <v>10.621387283237</v>
       </c>
       <c r="G76">
-        <v>29.6</v>
+        <v>23.7</v>
       </c>
       <c r="H76">
-        <v>14.8624794745484</v>
+        <v>14.072249589491</v>
       </c>
       <c r="I76">
-        <v>14.6703480589023</v>
+        <v>7.50502008032128</v>
       </c>
       <c r="J76">
-        <v>11.3840996168582</v>
+        <v>8.11781609195402</v>
       </c>
       <c r="K76" t="s">
         <v>12</v>
@@ -4078,34 +4083,34 @@
     </row>
     <row r="77" spans="1:11">
       <c r="A77" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B77" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C77">
         <v>64</v>
       </c>
       <c r="D77">
-        <v>21.8</v>
+        <v>14</v>
       </c>
       <c r="E77">
-        <v>24.288256227758</v>
+        <v>14.4009489916963</v>
       </c>
       <c r="F77">
-        <v>20.5202312138728</v>
+        <v>13.764450867052</v>
       </c>
       <c r="G77">
-        <v>39.2</v>
+        <v>30.3</v>
       </c>
       <c r="H77">
-        <v>26.1761083743842</v>
+        <v>18.7889983579639</v>
       </c>
       <c r="I77">
-        <v>21.7453145917001</v>
+        <v>13.1726907630522</v>
       </c>
       <c r="J77">
-        <v>19.3869731800766</v>
+        <v>11.7708333333333</v>
       </c>
       <c r="K77" t="s">
         <v>12</v>
@@ -4113,34 +4118,34 @@
     </row>
     <row r="78" spans="1:11">
       <c r="A78" t="s">
+        <v>100</v>
+      </c>
+      <c r="B78" t="s">
         <v>101</v>
       </c>
-      <c r="B78" t="s">
-        <v>102</v>
-      </c>
       <c r="C78">
         <v>64</v>
       </c>
       <c r="D78">
-        <v>12.7</v>
+        <v>13.3</v>
       </c>
       <c r="E78">
-        <v>10.3024911032029</v>
+        <v>10.6331553973903</v>
       </c>
       <c r="F78">
-        <v>13.9812138728324</v>
+        <v>14.7278420038536</v>
       </c>
       <c r="G78">
-        <v>27.7</v>
+        <v>29.6</v>
       </c>
       <c r="H78">
-        <v>17.3399014778325</v>
+        <v>14.8624794745484</v>
       </c>
       <c r="I78">
-        <v>13.3902275769746</v>
+        <v>14.6703480589023</v>
       </c>
       <c r="J78">
-        <v>9.47437739463602</v>
+        <v>11.3840996168582</v>
       </c>
       <c r="K78" t="s">
         <v>12</v>
@@ -4148,34 +4153,34 @@
     </row>
     <row r="79" spans="1:11">
       <c r="A79" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B79" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C79">
         <v>64</v>
       </c>
       <c r="D79">
-        <v>19.8</v>
+        <v>21.8</v>
       </c>
       <c r="E79">
-        <v>19.9614472123369</v>
+        <v>24.288256227758</v>
       </c>
       <c r="F79">
-        <v>19.6411368015414</v>
+        <v>20.5202312138728</v>
       </c>
       <c r="G79">
-        <v>37.4</v>
+        <v>39.2</v>
       </c>
       <c r="H79">
-        <v>26.7857142857143</v>
+        <v>26.1761083743842</v>
       </c>
       <c r="I79">
-        <v>19.3875502008032</v>
+        <v>21.7453145917001</v>
       </c>
       <c r="J79">
-        <v>15.9135536398467</v>
+        <v>19.3869731800766</v>
       </c>
       <c r="K79" t="s">
         <v>12</v>
@@ -4183,34 +4188,34 @@
     </row>
     <row r="80" spans="1:11">
       <c r="A80" t="s">
+        <v>103</v>
+      </c>
+      <c r="B80" t="s">
         <v>104</v>
       </c>
-      <c r="B80" t="s">
-        <v>105</v>
-      </c>
       <c r="C80">
         <v>64</v>
       </c>
       <c r="D80">
-        <v>11.6</v>
+        <v>12.7</v>
       </c>
       <c r="E80">
-        <v>10.0296559905101</v>
+        <v>10.3024911032029</v>
       </c>
       <c r="F80">
-        <v>12.3795761078998</v>
+        <v>13.9812138728324</v>
       </c>
       <c r="G80">
-        <v>26.5</v>
+        <v>27.7</v>
       </c>
       <c r="H80">
-        <v>14.9035303776683</v>
+        <v>17.3399014778325</v>
       </c>
       <c r="I80">
-        <v>11.1010709504685</v>
+        <v>13.3902275769746</v>
       </c>
       <c r="J80">
-        <v>9.92456896551724</v>
+        <v>9.47437739463602</v>
       </c>
       <c r="K80" t="s">
         <v>12</v>
@@ -4218,34 +4223,34 @@
     </row>
     <row r="81" spans="1:11">
       <c r="A81" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="B81" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C81">
         <v>64</v>
       </c>
       <c r="D81">
-        <v>20.7</v>
+        <v>19.8</v>
       </c>
       <c r="E81">
-        <v>21.3967971530249</v>
+        <v>19.9614472123369</v>
       </c>
       <c r="F81">
-        <v>20.3516377649326</v>
+        <v>19.6411368015414</v>
       </c>
       <c r="G81">
-        <v>38.8</v>
+        <v>37.4</v>
       </c>
       <c r="H81">
-        <v>26.2335796387521</v>
+        <v>26.7857142857143</v>
       </c>
       <c r="I81">
-        <v>21.0240963855422</v>
+        <v>19.3875502008032</v>
       </c>
       <c r="J81">
-        <v>17.283285440613</v>
+        <v>15.9135536398467</v>
       </c>
       <c r="K81" t="s">
         <v>12</v>
@@ -4253,34 +4258,34 @@
     </row>
     <row r="82" spans="1:11">
       <c r="A82" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B82" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C82">
         <v>64</v>
       </c>
       <c r="D82">
-        <v>13.7</v>
+        <v>11.6</v>
       </c>
       <c r="E82">
-        <v>13.1242586002372</v>
+        <v>10.0296559905101</v>
       </c>
       <c r="F82">
-        <v>13.9450867052023</v>
+        <v>12.3795761078998</v>
       </c>
       <c r="G82">
-        <v>28.9</v>
+        <v>26.5</v>
       </c>
       <c r="H82">
-        <v>16.6974548440066</v>
+        <v>14.9035303776683</v>
       </c>
       <c r="I82">
-        <v>12.6305220883534</v>
+        <v>11.1010709504685</v>
       </c>
       <c r="J82">
-        <v>12.617337164751</v>
+        <v>9.92456896551724</v>
       </c>
       <c r="K82" t="s">
         <v>12</v>
@@ -4288,34 +4293,34 @@
     </row>
     <row r="83" spans="1:11">
       <c r="A83" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B83" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C83">
-        <v>512</v>
+        <v>64</v>
       </c>
       <c r="D83">
-        <v>19.5</v>
+        <v>20.7</v>
       </c>
       <c r="E83">
-        <v>16.8431198102017</v>
+        <v>21.3967971530249</v>
       </c>
       <c r="F83">
-        <v>20.9898843930636</v>
+        <v>20.3516377649326</v>
       </c>
       <c r="G83">
-        <v>36.8</v>
+        <v>38.8</v>
       </c>
       <c r="H83">
-        <v>21.8390804597701</v>
+        <v>26.2335796387521</v>
       </c>
       <c r="I83">
-        <v>24.489625167336</v>
+        <v>21.0240963855422</v>
       </c>
       <c r="J83">
-        <v>14.6420019157088</v>
+        <v>17.283285440613</v>
       </c>
       <c r="K83" t="s">
         <v>12</v>
@@ -4323,34 +4328,34 @@
     </row>
     <row r="84" spans="1:11">
       <c r="A84" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B84" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C84">
         <v>64</v>
       </c>
       <c r="D84">
-        <v>23.2</v>
+        <v>13.7</v>
       </c>
       <c r="E84">
-        <v>22.2479240806643</v>
+        <v>13.1242586002372</v>
       </c>
       <c r="F84">
-        <v>23.6392100192678</v>
+        <v>13.9450867052023</v>
       </c>
       <c r="G84">
-        <v>40.3</v>
+        <v>28.9</v>
       </c>
       <c r="H84">
-        <v>28.2635467980296</v>
+        <v>16.6974548440066</v>
       </c>
       <c r="I84">
-        <v>24.7322623828648</v>
+        <v>12.6305220883534</v>
       </c>
       <c r="J84">
-        <v>19.0361590038314</v>
+        <v>12.617337164751</v>
       </c>
       <c r="K84" t="s">
         <v>12</v>
@@ -4358,34 +4363,34 @@
     </row>
     <row r="85" spans="1:11">
       <c r="A85" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B85" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C85">
         <v>512</v>
       </c>
       <c r="D85">
-        <v>26.2</v>
+        <v>19.5</v>
       </c>
       <c r="E85">
-        <v>26.8030842230131</v>
+        <v>16.8431198102017</v>
       </c>
       <c r="F85">
-        <v>25.8429672447013</v>
+        <v>20.9898843930636</v>
       </c>
       <c r="G85">
-        <v>44.5</v>
+        <v>36.8</v>
       </c>
       <c r="H85">
-        <v>30.4741379310345</v>
+        <v>21.8390804597701</v>
       </c>
       <c r="I85">
-        <v>30.1188085676038</v>
+        <v>24.489625167336</v>
       </c>
       <c r="J85">
-        <v>20.8572796934866</v>
+        <v>14.6420019157088</v>
       </c>
       <c r="K85" t="s">
         <v>12</v>
@@ -4393,34 +4398,34 @@
     </row>
     <row r="86" spans="1:11">
       <c r="A86" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B86" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C86">
         <v>64</v>
       </c>
       <c r="D86">
-        <v>17.6</v>
+        <v>23.2</v>
       </c>
       <c r="E86">
-        <v>16.4249703440095</v>
+        <v>22.2479240806643</v>
       </c>
       <c r="F86">
-        <v>18.1840077071291</v>
+        <v>23.6392100192678</v>
       </c>
       <c r="G86">
-        <v>34.5</v>
+        <v>40.3</v>
       </c>
       <c r="H86">
-        <v>19.9815270935961</v>
+        <v>28.2635467980296</v>
       </c>
       <c r="I86">
-        <v>18.5056894243641</v>
+        <v>24.7322623828648</v>
       </c>
       <c r="J86">
-        <v>15.4849137931035</v>
+        <v>19.0361590038314</v>
       </c>
       <c r="K86" t="s">
         <v>12</v>
@@ -4428,34 +4433,34 @@
     </row>
     <row r="87" spans="1:11">
       <c r="A87" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B87" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C87">
         <v>512</v>
       </c>
       <c r="D87">
-        <v>19.5</v>
+        <v>26.2</v>
       </c>
       <c r="E87">
-        <v>16.4739027283511</v>
+        <v>26.8030842230131</v>
       </c>
       <c r="F87">
-        <v>20.5924855491329</v>
+        <v>25.8429672447013</v>
       </c>
       <c r="G87">
-        <v>37.4</v>
+        <v>44.5</v>
       </c>
       <c r="H87">
-        <v>22.3173234811166</v>
+        <v>30.4741379310345</v>
       </c>
       <c r="I87">
-        <v>23.1492637215529</v>
+        <v>30.1188085676038</v>
       </c>
       <c r="J87">
-        <v>14.4312739463602</v>
+        <v>20.8572796934866</v>
       </c>
       <c r="K87" t="s">
         <v>12</v>
@@ -4463,34 +4468,34 @@
     </row>
     <row r="88" spans="1:11">
       <c r="A88" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B88" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C88">
         <v>64</v>
       </c>
       <c r="D88">
-        <v>29.6</v>
+        <v>17.6</v>
       </c>
       <c r="E88">
-        <v>31.6711150652432</v>
+        <v>16.4249703440095</v>
       </c>
       <c r="F88">
-        <v>28.5404624277457</v>
+        <v>18.1840077071291</v>
       </c>
       <c r="G88">
-        <v>47.6</v>
+        <v>34.5</v>
       </c>
       <c r="H88">
-        <v>34.997947454844</v>
+        <v>19.9815270935961</v>
       </c>
       <c r="I88">
-        <v>30.5856760374833</v>
+        <v>18.5056894243641</v>
       </c>
       <c r="J88">
-        <v>25.838122605364</v>
+        <v>15.4849137931035</v>
       </c>
       <c r="K88" t="s">
         <v>12</v>
@@ -4498,34 +4503,34 @@
     </row>
     <row r="89" spans="1:11">
       <c r="A89" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B89" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C89">
         <v>512</v>
       </c>
       <c r="D89">
-        <v>31.4</v>
+        <v>19.5</v>
       </c>
       <c r="E89">
-        <v>31.2574139976275</v>
+        <v>16.4739027283511</v>
       </c>
       <c r="F89">
-        <v>31.5149325626204</v>
+        <v>20.5924855491329</v>
       </c>
       <c r="G89">
-        <v>49.6</v>
+        <v>37.4</v>
       </c>
       <c r="H89">
-        <v>34.3534482758621</v>
+        <v>22.3173234811166</v>
       </c>
       <c r="I89">
-        <v>36.3922356091031</v>
+        <v>23.1492637215529</v>
       </c>
       <c r="J89">
-        <v>26.1613984674329</v>
+        <v>14.4312739463602</v>
       </c>
       <c r="K89" t="s">
         <v>12</v>
@@ -4533,34 +4538,34 @@
     </row>
     <row r="90" spans="1:11">
       <c r="A90" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B90" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C90">
         <v>64</v>
       </c>
       <c r="D90">
-        <v>15.6</v>
+        <v>29.6</v>
       </c>
       <c r="E90">
-        <v>14.629300118624</v>
+        <v>31.6711150652432</v>
       </c>
       <c r="F90">
-        <v>16.0765895953757</v>
+        <v>28.5404624277457</v>
       </c>
       <c r="G90">
-        <v>32.6</v>
+        <v>47.6</v>
       </c>
       <c r="H90">
-        <v>18.1547619047619</v>
+        <v>34.997947454844</v>
       </c>
       <c r="I90">
-        <v>15.8467202141901</v>
+        <v>30.5856760374833</v>
       </c>
       <c r="J90">
-        <v>13.860153256705</v>
+        <v>25.838122605364</v>
       </c>
       <c r="K90" t="s">
         <v>12</v>
@@ -4568,34 +4573,34 @@
     </row>
     <row r="91" spans="1:11">
       <c r="A91" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B91" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C91">
         <v>512</v>
       </c>
       <c r="D91">
-        <v>12.2</v>
+        <v>31.4</v>
       </c>
       <c r="E91">
-        <v>11.0513048635824</v>
+        <v>31.2574139976275</v>
       </c>
       <c r="F91">
-        <v>12.7890173410405</v>
+        <v>31.5149325626204</v>
       </c>
       <c r="G91">
-        <v>28.5</v>
+        <v>49.6</v>
       </c>
       <c r="H91">
-        <v>13.9326765188834</v>
+        <v>34.3534482758621</v>
       </c>
       <c r="I91">
-        <v>11.3922356091031</v>
+        <v>36.3922356091031</v>
       </c>
       <c r="J91">
-        <v>11.7181513409962</v>
+        <v>26.1613984674329</v>
       </c>
       <c r="K91" t="s">
         <v>12</v>
@@ -4603,34 +4608,34 @@
     </row>
     <row r="92" spans="1:11">
       <c r="A92" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B92" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C92">
         <v>64</v>
       </c>
       <c r="D92">
-        <v>25.8</v>
+        <v>15.6</v>
       </c>
       <c r="E92">
-        <v>27.5385527876631</v>
+        <v>14.629300118624</v>
       </c>
       <c r="F92">
-        <v>24.8554913294798</v>
+        <v>16.0765895953757</v>
       </c>
       <c r="G92">
-        <v>43.9</v>
+        <v>32.6</v>
       </c>
       <c r="H92">
-        <v>31.2828407224959</v>
+        <v>18.1547619047619</v>
       </c>
       <c r="I92">
-        <v>24.894578313253</v>
+        <v>15.8467202141901</v>
       </c>
       <c r="J92">
-        <v>23.2447318007663</v>
+        <v>13.860153256705</v>
       </c>
       <c r="K92" t="s">
         <v>12</v>
@@ -4638,34 +4643,34 @@
     </row>
     <row r="93" spans="1:11">
       <c r="A93" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B93" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C93">
         <v>512</v>
       </c>
       <c r="D93">
-        <v>23.9</v>
+        <v>12.2</v>
       </c>
       <c r="E93">
-        <v>24.6975088967971</v>
+        <v>11.0513048635824</v>
       </c>
       <c r="F93">
-        <v>23.3983622350674</v>
+        <v>12.7890173410405</v>
       </c>
       <c r="G93">
-        <v>41.5</v>
+        <v>28.5</v>
       </c>
       <c r="H93">
-        <v>29.5402298850575</v>
+        <v>13.9326765188834</v>
       </c>
       <c r="I93">
-        <v>24.4996653279786</v>
+        <v>11.3922356091031</v>
       </c>
       <c r="J93">
-        <v>20.0766283524904</v>
+        <v>11.7181513409962</v>
       </c>
       <c r="K93" t="s">
         <v>12</v>
@@ -4673,34 +4678,34 @@
     </row>
     <row r="94" spans="1:11">
       <c r="A94" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B94" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C94">
         <v>64</v>
       </c>
       <c r="D94">
-        <v>16.3</v>
+        <v>25.8</v>
       </c>
       <c r="E94">
-        <v>15.2698695136417</v>
+        <v>27.5385527876631</v>
       </c>
       <c r="F94">
-        <v>16.7991329479769</v>
+        <v>24.8554913294798</v>
       </c>
       <c r="G94">
-        <v>33</v>
+        <v>43.9</v>
       </c>
       <c r="H94">
-        <v>18.9573070607553</v>
+        <v>31.2828407224959</v>
       </c>
       <c r="I94">
-        <v>15.9906291834003</v>
+        <v>24.894578313253</v>
       </c>
       <c r="J94">
-        <v>14.8838601532567</v>
+        <v>23.2447318007663</v>
       </c>
       <c r="K94" t="s">
         <v>12</v>
@@ -4708,34 +4713,34 @@
     </row>
     <row r="95" spans="1:11">
       <c r="A95" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B95" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C95">
         <v>512</v>
       </c>
       <c r="D95">
-        <v>14</v>
+        <v>23.9</v>
       </c>
       <c r="E95">
-        <v>12.8959074733096</v>
+        <v>24.6975088967971</v>
       </c>
       <c r="F95">
-        <v>14.5472061657033</v>
+        <v>23.3983622350674</v>
       </c>
       <c r="G95">
-        <v>30.6</v>
+        <v>41.5</v>
       </c>
       <c r="H95">
-        <v>15.7717569786535</v>
+        <v>29.5402298850575</v>
       </c>
       <c r="I95">
-        <v>13.9574966532798</v>
+        <v>24.4996653279786</v>
       </c>
       <c r="J95">
-        <v>12.9214559386973</v>
+        <v>20.0766283524904</v>
       </c>
       <c r="K95" t="s">
         <v>12</v>
@@ -4743,34 +4748,34 @@
     </row>
     <row r="96" spans="1:11">
       <c r="A96" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B96" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C96">
         <v>64</v>
       </c>
       <c r="D96">
-        <v>26.7</v>
+        <v>16.3</v>
       </c>
       <c r="E96">
-        <v>27.2553380782918</v>
+        <v>15.2698695136417</v>
       </c>
       <c r="F96">
-        <v>26.4210019267823</v>
+        <v>16.7991329479769</v>
       </c>
       <c r="G96">
-        <v>45.1</v>
+        <v>33</v>
       </c>
       <c r="H96">
-        <v>30.1128899835796</v>
+        <v>18.9573070607553</v>
       </c>
       <c r="I96">
-        <v>27.8815261044177</v>
+        <v>15.9906291834003</v>
       </c>
       <c r="J96">
-        <v>23.8960727969349</v>
+        <v>14.8838601532567</v>
       </c>
       <c r="K96" t="s">
         <v>12</v>
@@ -4778,34 +4783,34 @@
     </row>
     <row r="97" spans="1:11">
       <c r="A97" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B97" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C97">
         <v>512</v>
       </c>
       <c r="D97">
-        <v>25.1</v>
+        <v>14</v>
       </c>
       <c r="E97">
-        <v>26.4798339264531</v>
+        <v>12.8959074733096</v>
       </c>
       <c r="F97">
-        <v>24.3376685934489</v>
+        <v>14.5472061657033</v>
       </c>
       <c r="G97">
-        <v>43.4</v>
+        <v>30.6</v>
       </c>
       <c r="H97">
-        <v>27.4466338259442</v>
+        <v>15.7717569786535</v>
       </c>
       <c r="I97">
-        <v>25.563922356091</v>
+        <v>13.9574966532798</v>
       </c>
       <c r="J97">
-        <v>23.3764367816092</v>
+        <v>12.9214559386973</v>
       </c>
       <c r="K97" t="s">
         <v>12</v>
@@ -4813,34 +4818,34 @@
     </row>
     <row r="98" spans="1:11">
       <c r="A98" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B98" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C98">
         <v>64</v>
       </c>
-      <c r="D98" t="s">
-        <v>12</v>
-      </c>
-      <c r="E98" t="s">
-        <v>12</v>
-      </c>
-      <c r="F98" t="s">
-        <v>12</v>
-      </c>
-      <c r="G98" t="s">
-        <v>12</v>
-      </c>
-      <c r="H98" t="s">
-        <v>12</v>
-      </c>
-      <c r="I98" t="s">
-        <v>12</v>
-      </c>
-      <c r="J98" t="s">
-        <v>12</v>
+      <c r="D98">
+        <v>26.7</v>
+      </c>
+      <c r="E98">
+        <v>27.2553380782918</v>
+      </c>
+      <c r="F98">
+        <v>26.4210019267823</v>
+      </c>
+      <c r="G98">
+        <v>45.1</v>
+      </c>
+      <c r="H98">
+        <v>30.1128899835796</v>
+      </c>
+      <c r="I98">
+        <v>27.8815261044177</v>
+      </c>
+      <c r="J98">
+        <v>23.8960727969349</v>
       </c>
       <c r="K98" t="s">
         <v>12</v>
@@ -4848,106 +4853,208 @@
     </row>
     <row r="99" spans="1:11">
       <c r="A99" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B99" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C99">
         <v>512</v>
       </c>
-      <c r="D99" t="s">
-        <v>12</v>
-      </c>
-      <c r="E99" t="s">
-        <v>12</v>
-      </c>
-      <c r="F99" t="s">
-        <v>12</v>
-      </c>
-      <c r="G99" t="s">
-        <v>12</v>
-      </c>
-      <c r="H99" t="s">
-        <v>12</v>
-      </c>
-      <c r="I99" t="s">
-        <v>12</v>
-      </c>
-      <c r="J99" t="s">
-        <v>12</v>
+      <c r="D99">
+        <v>25.1</v>
+      </c>
+      <c r="E99">
+        <v>26.4798339264531</v>
+      </c>
+      <c r="F99">
+        <v>24.3376685934489</v>
+      </c>
+      <c r="G99">
+        <v>43.4</v>
+      </c>
+      <c r="H99">
+        <v>27.4466338259442</v>
+      </c>
+      <c r="I99">
+        <v>25.563922356091</v>
+      </c>
+      <c r="J99">
+        <v>23.3764367816092</v>
       </c>
       <c r="K99" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="100" spans="1:11">
-      <c r="A100" t="s">
-        <v>72</v>
-      </c>
-      <c r="B100" t="s">
-        <v>105</v>
-      </c>
-      <c r="C100">
-        <v>64</v>
-      </c>
-      <c r="D100" t="s">
-        <v>12</v>
-      </c>
-      <c r="E100" t="s">
-        <v>12</v>
-      </c>
-      <c r="F100" t="s">
-        <v>12</v>
-      </c>
-      <c r="G100" t="s">
-        <v>12</v>
-      </c>
-      <c r="H100" t="s">
-        <v>12</v>
-      </c>
-      <c r="I100" t="s">
-        <v>12</v>
-      </c>
-      <c r="J100" t="s">
-        <v>12</v>
-      </c>
-      <c r="K100" t="s">
-        <v>12</v>
+      <c r="A100" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="101" spans="1:11">
       <c r="A101" t="s">
+        <v>71</v>
+      </c>
+      <c r="B101" t="s">
+        <v>106</v>
+      </c>
+      <c r="C101">
+        <v>64</v>
+      </c>
+      <c r="D101">
+        <v>20.7</v>
+      </c>
+      <c r="E101">
+        <v>20.3929418742586</v>
+      </c>
+      <c r="F101">
+        <v>20.8694605009634</v>
+      </c>
+      <c r="G101">
+        <v>39.3</v>
+      </c>
+      <c r="H101">
+        <v>20.7101806239737</v>
+      </c>
+      <c r="I101">
+        <v>23.1007362784471</v>
+      </c>
+      <c r="J101">
+        <v>18.9810823754789</v>
+      </c>
+      <c r="K101" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11">
+      <c r="A102" t="s">
+        <v>71</v>
+      </c>
+      <c r="B102" t="s">
+        <v>106</v>
+      </c>
+      <c r="C102">
+        <v>512</v>
+      </c>
+      <c r="D102">
+        <v>30.3</v>
+      </c>
+      <c r="E102">
+        <v>26.9098457888493</v>
+      </c>
+      <c r="F102">
+        <v>32.1772639691715</v>
+      </c>
+      <c r="G102">
+        <v>48.8</v>
+      </c>
+      <c r="H102">
+        <v>35.4330870279146</v>
+      </c>
+      <c r="I102">
+        <v>36.5026773761713</v>
+      </c>
+      <c r="J102">
+        <v>22.929837164751</v>
+      </c>
+      <c r="K102" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11">
+      <c r="A103" t="s">
         <v>72</v>
       </c>
-      <c r="B101" t="s">
-        <v>105</v>
-      </c>
-      <c r="C101">
+      <c r="B103" t="s">
+        <v>106</v>
+      </c>
+      <c r="C103">
+        <v>64</v>
+      </c>
+      <c r="D103">
+        <v>30.6</v>
+      </c>
+      <c r="E103">
+        <v>32.6927639383155</v>
+      </c>
+      <c r="F103">
+        <v>29.5038535645472</v>
+      </c>
+      <c r="G103">
+        <v>48.9</v>
+      </c>
+      <c r="H103">
+        <v>34.7906403940887</v>
+      </c>
+      <c r="I103">
+        <v>30.3647925033467</v>
+      </c>
+      <c r="J103">
+        <v>28.3788314176245</v>
+      </c>
+      <c r="K103" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11">
+      <c r="A104" t="s">
+        <v>72</v>
+      </c>
+      <c r="B104" t="s">
+        <v>106</v>
+      </c>
+      <c r="C104">
         <v>512</v>
       </c>
-      <c r="D101" t="s">
-        <v>12</v>
-      </c>
-      <c r="E101" t="s">
-        <v>12</v>
-      </c>
-      <c r="F101" t="s">
-        <v>12</v>
-      </c>
-      <c r="G101" t="s">
-        <v>12</v>
-      </c>
-      <c r="H101" t="s">
-        <v>12</v>
-      </c>
-      <c r="I101" t="s">
-        <v>12</v>
-      </c>
-      <c r="J101" t="s">
-        <v>12</v>
-      </c>
-      <c r="K101" t="s">
+      <c r="D104">
+        <v>39.1</v>
+      </c>
+      <c r="E104">
+        <v>39.3609134045077</v>
+      </c>
+      <c r="F104">
+        <v>38.9571290944123</v>
+      </c>
+      <c r="G104">
+        <v>55.9</v>
+      </c>
+      <c r="H104">
+        <v>50.309934318555</v>
+      </c>
+      <c r="I104">
+        <v>41.7553547523427</v>
+      </c>
+      <c r="J104">
+        <v>30.6585249042146</v>
+      </c>
+      <c r="K104" t="s">
         <v>12</v>
       </c>
     </row>

--- a/figs/exps/performance_parsed.xlsx
+++ b/figs/exps/performance_parsed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K107"/>
+  <dimension ref="A1:K110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2514,52 +2514,93 @@
         <v>16</v>
       </c>
       <c r="D52" t="n">
-        <v>11.3</v>
+        <v>7.8</v>
       </c>
       <c r="E52" t="n">
-        <v>13.02935943060498</v>
+        <v>7.959667852906287</v>
       </c>
       <c r="F52" t="n">
-        <v>10.34441233140655</v>
+        <v>7.755298651252408</v>
       </c>
       <c r="G52" t="n">
-        <v>25.8</v>
+        <v>18.6</v>
       </c>
       <c r="H52" t="n">
-        <v>14.12972085385879</v>
+        <v>8.442118226600986</v>
       </c>
       <c r="I52" t="n">
-        <v>9.421017402945115</v>
+        <v>6.60475234270415</v>
       </c>
       <c r="J52" t="n">
-        <v>10.96503831417625</v>
+        <v>8.342911877394636</v>
       </c>
       <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Thinking Model</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>VITA-1.5-sub</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Sampling Parameter
+temperature = 0.01
+top_p = None
+num_beams = 1
+</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>8</v>
+      </c>
+      <c r="D53" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="E53" t="n">
+        <v>13.02935943060498</v>
+      </c>
+      <c r="F53" t="n">
+        <v>10.34441233140655</v>
+      </c>
+      <c r="G53" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="H53" t="n">
+        <v>14.12972085385879</v>
+      </c>
+      <c r="I53" t="n">
+        <v>9.421017402945115</v>
+      </c>
+      <c r="J53" t="n">
+        <v>10.96503831417625</v>
+      </c>
       <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Thinking Model</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>Qwen3vl-4B-think</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>temperature=1.0, 
 max_new_tokens=40960,
@@ -2569,39 +2610,39 @@
 top_k=20</t>
         </is>
       </c>
-      <c r="C54" t="n">
-        <v>64</v>
-      </c>
-      <c r="D54" t="n">
+      <c r="C55" t="n">
+        <v>64</v>
+      </c>
+      <c r="D55" t="n">
         <v>11.6</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E55" t="n">
         <v>9.676749703440095</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F55" t="n">
         <v>12.58429672447014</v>
       </c>
-      <c r="G54" t="n">
+      <c r="G55" t="n">
         <v>26.2</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H55" t="n">
         <v>14.97947454844007</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I55" t="n">
         <v>11.30354752342704</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J55" t="n">
         <v>9.755747126436782</v>
       </c>
-      <c r="K54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="K55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Qwen3vl-4B-think-sub</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>temperature=1.0, 
 max_new_tokens=40960,
@@ -2611,39 +2652,90 @@
 top_k=20</t>
         </is>
       </c>
-      <c r="C55" t="n">
-        <v>64</v>
-      </c>
-      <c r="D55" t="n">
+      <c r="C56" t="n">
+        <v>64</v>
+      </c>
+      <c r="D56" t="n">
         <v>18.2</v>
       </c>
-      <c r="E55" t="n">
-        <v>18.57354685646501</v>
-      </c>
-      <c r="F55" t="n">
-        <v>17.94315992292871</v>
-      </c>
-      <c r="G55" t="n">
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="n">
         <v>35.3</v>
       </c>
-      <c r="H55" t="n">
-        <v>23.26765188834154</v>
-      </c>
-      <c r="I55" t="n">
-        <v>16.57797858099063</v>
-      </c>
-      <c r="J55" t="n">
-        <v>16.32303639846743</v>
-      </c>
-      <c r="K55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>{
+"final_rating": {
+"level_1": 23.267651888341543,
+"level_2": 16.57797858099063,
+"level_3": 16.323036398467433,
+"relevance_score": 17.943159922928707,
+"relevance_linear_score": 32.46628131021195,
+"logic_score": 18.573546856465008,
+"total": 18.164583333333333
+},
+"second_head_rating": {
+"Complex Plot Comprehension": 16.460727969348657,
+"Physical World Reasoning": 10.787037037037038,
+"Video-Based Knowledge Acquisition": 27.174329501915707,
+"Temporal Reasoning": 17.333333333333336,
+"Order": 23.827777777777776,
+"Change": 13.822115384615385,
+"Social Behavior Analysis": 10.883333333333333,
+"Action &amp; Motion": 9.98134328358209,
+"Frame-Only": 20.499131944444446,
+"Frames &amp; Audio": 25.751557632398754
+},
+"third_head_rating": {
+"Symbolic/Metaphorical Interpretation": 16.185897435897434,
+"Counterfactual Reasoning": 17.261904761904763,
+"Entity Persistence Tracking": 9.75,
+"Professional Knowledge Acquisition": 27.395833333333336,
+"High-Order Narrative Deconstruction": 12.380952380952381,
+"Narrative Turning Point Detection": 15.07936507936508,
+"Causal Reasoning": 19.734848484848484,
+"Event Sequence Ordering": 25.862068965517242,
+"Scene Transformation Detection": 14.583333333333334,
+"Entity Attribute Change Detection": 15.5,
+"Object Appearance Ordering": 27.546296296296298,
+"Individual Social Cognition": 14.333333333333332,
+"Collective Dynamics Analysis": 9.83974358974359,
+"General Skills Acquisition": 26.947674418604652,
+"Spatial Understanding": 5.15,
+"Counterintuitive Comprehension": 11.889880952380953,
+"Fine-Grained Action Recognition": 5.833333333333333,
+"Visual Recognition": 36.955128205128204,
+"Dyadic Interaction Dynamics": 8.42013888888889,
+"Audio-Guided Visual Description": 13.75,
+"Narrative Cloze Inference": 22.87280701754386,
+"Future Event Prediction": 13.731060606060606,
+"Entity Existence Change Detection": 10.416666666666666,
+"Temporal Periodicity Detection": 15.438596491228068,
+"Repetitive Action Counting": 3.125,
+"Motion Trajectory Estimation": 8.035714285714286,
+"Basic Counting": 10.096153846153847,
+"Numerical Calculation": 8.521505376344086,
+"Vision-Guided Audio Description": 20.454545454545453,
+"Visual-Audio Collaborative Reasoning": 34.95614035087719,
+"Temporal Action Localization": 17.5,
+"Motion Properties Analysis": 16.015625,
+"Cross-Modal Semantic Consistency": 28.78787878787879
+}
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Qwen3vl-8B-think</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>temperature=1.0, 
 max_new_tokens=40960,
@@ -2653,39 +2745,39 @@
 top_k=20</t>
         </is>
       </c>
-      <c r="C56" t="n">
-        <v>64</v>
-      </c>
-      <c r="D56" t="n">
+      <c r="C57" t="n">
+        <v>64</v>
+      </c>
+      <c r="D57" t="n">
         <v>11.8</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E57" t="n">
         <v>10.01779359430605</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F57" t="n">
         <v>12.72880539499037</v>
       </c>
-      <c r="G56" t="n">
+      <c r="G57" t="n">
         <v>27</v>
       </c>
-      <c r="H56" t="n">
+      <c r="H57" t="n">
         <v>13.10550082101806</v>
       </c>
-      <c r="I56" t="n">
+      <c r="I57" t="n">
         <v>11.84571619812584</v>
       </c>
-      <c r="J56" t="n">
+      <c r="J57" t="n">
         <v>10.95186781609195</v>
       </c>
-      <c r="K56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="K57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Qwen3vl-8B-think</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>temperature=1.0, 
 max_new_tokens=40960,
@@ -2695,39 +2787,39 @@
 top_k=20</t>
         </is>
       </c>
-      <c r="C57" t="n">
+      <c r="C58" t="n">
         <v>512</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D58" t="n">
         <v>14.4</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E58" t="n">
         <v>13.01008303677343</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F58" t="n">
         <v>15.07707129094412</v>
       </c>
-      <c r="G57" t="n">
+      <c r="G58" t="n">
         <v>29.7</v>
       </c>
-      <c r="H57" t="n">
+      <c r="H58" t="n">
         <v>16.97249589490969</v>
       </c>
-      <c r="I57" t="n">
+      <c r="I58" t="n">
         <v>16.74196787148594</v>
       </c>
-      <c r="J57" t="n">
+      <c r="J58" t="n">
         <v>11.11111111111111</v>
       </c>
-      <c r="K57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="K58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>Qwen3vl-8B-think-sub</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>temperature=1.0, 
 max_new_tokens=40960,
@@ -2737,39 +2829,39 @@
 top_k=20</t>
         </is>
       </c>
-      <c r="C58" t="n">
-        <v>64</v>
-      </c>
-      <c r="D58" t="n">
+      <c r="C59" t="n">
+        <v>64</v>
+      </c>
+      <c r="D59" t="n">
         <v>19.7</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E59" t="n">
         <v>20.50266903914591</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F59" t="n">
         <v>19.18352601156069</v>
       </c>
-      <c r="G58" t="n">
+      <c r="G59" t="n">
         <v>37.2</v>
       </c>
-      <c r="H58" t="n">
+      <c r="H59" t="n">
         <v>23.87110016420361</v>
       </c>
-      <c r="I58" t="n">
+      <c r="I59" t="n">
         <v>19.24364123159304</v>
       </c>
-      <c r="J58" t="n">
+      <c r="J59" t="n">
         <v>17.47126436781609</v>
       </c>
-      <c r="K58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="K59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Qwen3vl-8B-think-sub</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>temperature=1.0, 
 max_new_tokens=40960,
@@ -2779,39 +2871,39 @@
 top_k=20</t>
         </is>
       </c>
-      <c r="C59" t="n">
+      <c r="C60" t="n">
         <v>512</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D60" t="n">
         <v>20.2</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E60" t="n">
         <v>20.25800711743772</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F60" t="n">
         <v>20.11078998073218</v>
       </c>
-      <c r="G59" t="n">
+      <c r="G60" t="n">
         <v>37.3</v>
       </c>
-      <c r="H59" t="n">
+      <c r="H60" t="n">
         <v>23.46264367816092</v>
       </c>
-      <c r="I59" t="n">
+      <c r="I60" t="n">
         <v>21.35709504685408</v>
       </c>
-      <c r="J59" t="n">
+      <c r="J60" t="n">
         <v>17.38266283524904</v>
       </c>
-      <c r="K59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="K60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Qwen3vl-30B-A3B-Think</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>temperature: 1.0
 top_k: 20
@@ -2821,39 +2913,39 @@
 presence_penalty: 0.0</t>
         </is>
       </c>
-      <c r="C60" t="n">
-        <v>64</v>
-      </c>
-      <c r="D60" t="n">
+      <c r="C61" t="n">
+        <v>64</v>
+      </c>
+      <c r="D61" t="n">
         <v>13.5</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E61" t="n">
         <v>12.46886120996441</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F61" t="n">
         <v>14.10163776493256</v>
       </c>
-      <c r="G60" t="n">
+      <c r="G61" t="n">
         <v>29.4</v>
       </c>
-      <c r="H60" t="n">
+      <c r="H61" t="n">
         <v>17.43431855500821</v>
       </c>
-      <c r="I60" t="n">
+      <c r="I61" t="n">
         <v>13.71987951807229</v>
       </c>
-      <c r="J60" t="n">
+      <c r="J61" t="n">
         <v>11.11230842911877</v>
       </c>
-      <c r="K60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="K61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>Qwen3vl-30B-A3B-Think</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>temperature: 1.0
 top_k: 20
@@ -2863,39 +2955,39 @@
 presence_penalty: 0.0</t>
         </is>
       </c>
-      <c r="C61" t="n">
+      <c r="C62" t="n">
         <v>512</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D62" t="n">
         <v>13.2</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E62" t="n">
         <v>10.37663107947806</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F62" t="n">
         <v>14.76396917148362</v>
       </c>
-      <c r="G61" t="n">
+      <c r="G62" t="n">
         <v>29.5</v>
       </c>
-      <c r="H61" t="n">
+      <c r="H62" t="n">
         <v>16.93965517241379</v>
       </c>
-      <c r="I61" t="n">
+      <c r="I62" t="n">
         <v>14.66532797858099</v>
       </c>
-      <c r="J61" t="n">
+      <c r="J62" t="n">
         <v>10.02274904214559</v>
       </c>
-      <c r="K61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="K62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>Qwen3vl-30B-A3B-Think-sub</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>temperature: 1.0
 top_k: 20
@@ -2905,39 +2997,39 @@
 presence_penalty: 0.0</t>
         </is>
       </c>
-      <c r="C62" t="n">
-        <v>64</v>
-      </c>
-      <c r="D62" t="n">
+      <c r="C63" t="n">
+        <v>64</v>
+      </c>
+      <c r="D63" t="n">
         <v>21.1</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E63" t="n">
         <v>22.59638196915777</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F63" t="n">
         <v>20.21917148362235</v>
       </c>
-      <c r="G62" t="n">
+      <c r="G63" t="n">
         <v>38.6</v>
       </c>
-      <c r="H62" t="n">
+      <c r="H63" t="n">
         <v>26.97044334975369</v>
       </c>
-      <c r="I62" t="n">
+      <c r="I63" t="n">
         <v>21.09939759036144</v>
       </c>
-      <c r="J62" t="n">
+      <c r="J63" t="n">
         <v>17.57064176245211</v>
       </c>
-      <c r="K62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="K63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Qwen3vl-30B-A3B-Think-sub</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>temperature: 1.0
 top_k: 20
@@ -2947,78 +3039,78 @@
 presence_penalty: 0.0</t>
         </is>
       </c>
-      <c r="C63" t="n">
+      <c r="C64" t="n">
         <v>512</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D64" t="n">
         <v>22.1</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E64" t="n">
         <v>22.80397390272835</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F64" t="n">
         <v>21.70038535645472</v>
       </c>
-      <c r="G63" t="n">
+      <c r="G64" t="n">
         <v>39.8</v>
       </c>
-      <c r="H63" t="n">
+      <c r="H64" t="n">
         <v>27.61904761904762</v>
       </c>
-      <c r="I63" t="n">
+      <c r="I64" t="n">
         <v>22.38453815261044</v>
       </c>
-      <c r="J63" t="n">
+      <c r="J64" t="n">
         <v>18.64942528735632</v>
       </c>
-      <c r="K63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="K64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>Qwen3-Omni-30B-A3B-Think</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>temperature: 0.6
 top_p: 0.95
 max_tokens: 16384</t>
         </is>
       </c>
-      <c r="C64" t="n">
-        <v>64</v>
-      </c>
-      <c r="D64" t="n">
+      <c r="C65" t="n">
+        <v>64</v>
+      </c>
+      <c r="D65" t="n">
         <v>17.7</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E65" t="n">
         <v>18.41933570581257</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F65" t="n">
         <v>17.24470134874759</v>
       </c>
-      <c r="G64" t="n">
+      <c r="G65" t="n">
         <v>35.8</v>
       </c>
-      <c r="H64" t="n">
+      <c r="H65" t="n">
         <v>23.55500821018062</v>
       </c>
-      <c r="I64" t="n">
+      <c r="I65" t="n">
         <v>15.48527443105756</v>
       </c>
-      <c r="J64" t="n">
+      <c r="J65" t="n">
         <v>15.77107279693486</v>
       </c>
-      <c r="K64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="K65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>Qwen3-Omni-30B-A3B-Think-wo_audio</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>temperature: 1.0
 top_k: 20
@@ -3028,78 +3120,78 @@
 presence_penalty: 0.0</t>
         </is>
       </c>
-      <c r="C65" t="n">
-        <v>64</v>
-      </c>
-      <c r="D65" t="n">
+      <c r="C66" t="n">
+        <v>64</v>
+      </c>
+      <c r="D66" t="n">
         <v>12.6</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E66" t="n">
         <v>11.38048635824437</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F66" t="n">
         <v>13.30684007707129</v>
       </c>
-      <c r="G65" t="n">
+      <c r="G66" t="n">
         <v>28.6</v>
       </c>
-      <c r="H65" t="n">
+      <c r="H66" t="n">
         <v>15.79844006568145</v>
       </c>
-      <c r="I65" t="n">
+      <c r="I66" t="n">
         <v>12.27409638554217</v>
       </c>
-      <c r="J65" t="n">
+      <c r="J66" t="n">
         <v>11.03687739463602</v>
       </c>
-      <c r="K65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="K66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>Qwen3-Omni-30B-A3B-Think-sub</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>temperature: 0.6
 top_p: 0.95
 max_tokens: 16384</t>
         </is>
       </c>
-      <c r="C66" t="n">
-        <v>64</v>
-      </c>
-      <c r="D66" t="n">
+      <c r="C67" t="n">
+        <v>64</v>
+      </c>
+      <c r="D67" t="n">
         <v>19.5</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E67" t="n">
         <v>21.23962040332147</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F67" t="n">
         <v>18.59344894026975</v>
       </c>
-      <c r="G66" t="n">
+      <c r="G67" t="n">
         <v>36.5</v>
       </c>
-      <c r="H66" t="n">
+      <c r="H67" t="n">
         <v>24.72290640394089</v>
       </c>
-      <c r="I66" t="n">
+      <c r="I67" t="n">
         <v>17.48661311914324</v>
       </c>
-      <c r="J66" t="n">
+      <c r="J67" t="n">
         <v>17.94659961685824</v>
       </c>
-      <c r="K66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="K67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>Qwen3-Omni-30B-A3B-Think-sub-wo_audio</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>temperature: 1.0
 top_k: 20
@@ -3109,39 +3201,39 @@
 presence_penalty: 0.0</t>
         </is>
       </c>
-      <c r="C67" t="n">
-        <v>64</v>
-      </c>
-      <c r="D67" t="n">
+      <c r="C68" t="n">
+        <v>64</v>
+      </c>
+      <c r="D68" t="n">
         <v>18.3</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E68" t="n">
         <v>20.43149466192171</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F68" t="n">
         <v>17.1242774566474</v>
       </c>
-      <c r="G67" t="n">
+      <c r="G68" t="n">
         <v>36</v>
       </c>
-      <c r="H67" t="n">
+      <c r="H68" t="n">
         <v>23.30254515599343</v>
       </c>
-      <c r="I67" t="n">
+      <c r="I68" t="n">
         <v>15.82663989290495</v>
       </c>
-      <c r="J67" t="n">
+      <c r="J68" t="n">
         <v>17.11925287356322</v>
       </c>
-      <c r="K67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="K68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>Qwen3-VL-235B-A22B-Think</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>temperature: 1.0
 top_k: 20
@@ -3151,39 +3243,39 @@
 presence_penalty: 0.0</t>
         </is>
       </c>
-      <c r="C68" t="n">
-        <v>64</v>
-      </c>
-      <c r="D68" t="n">
+      <c r="C69" t="n">
+        <v>64</v>
+      </c>
+      <c r="D69" t="n">
         <v>15.9</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E69" t="n">
         <v>13.43861209964413</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F69" t="n">
         <v>17.23265895953757</v>
       </c>
-      <c r="G68" t="n">
+      <c r="G69" t="n">
         <v>33.3</v>
       </c>
-      <c r="H68" t="n">
+      <c r="H69" t="n">
         <v>19.07840722495895</v>
       </c>
-      <c r="I68" t="n">
+      <c r="I69" t="n">
         <v>16.7921686746988</v>
       </c>
-      <c r="J68" t="n">
+      <c r="J69" t="n">
         <v>13.40756704980843</v>
       </c>
-      <c r="K68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="K69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>Qwen3-VL-235B-A22B-Think</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>temperature: 1.0
 top_k: 20
@@ -3193,39 +3285,39 @@
 presence_penalty: 0.0</t>
         </is>
       </c>
-      <c r="C69" t="n">
+      <c r="C70" t="n">
         <v>512</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D70" t="n">
         <v>19</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E70" t="n">
         <v>16.46797153024911</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F70" t="n">
         <v>20.3757225433526</v>
       </c>
-      <c r="G69" t="n">
+      <c r="G70" t="n">
         <v>36.8</v>
       </c>
-      <c r="H69" t="n">
+      <c r="H70" t="n">
         <v>21.36083743842364</v>
       </c>
-      <c r="I69" t="n">
+      <c r="I70" t="n">
         <v>23.38855421686747</v>
       </c>
-      <c r="J69" t="n">
+      <c r="J70" t="n">
         <v>14.48994252873563</v>
       </c>
-      <c r="K69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="K70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>Qwen3-VL-235B-A22B-Think-random</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>temperature: 1.0
 top_k: 20
@@ -3235,39 +3327,39 @@
 presence_penalty: 0.0</t>
         </is>
       </c>
-      <c r="C70" t="n">
+      <c r="C71" t="n">
         <v>512</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D71" t="n">
         <v>12.9</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E71" t="n">
         <v>12.17674970344009</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F71" t="n">
         <v>13.33092485549133</v>
       </c>
-      <c r="G70" t="n">
+      <c r="G71" t="n">
         <v>29.3</v>
       </c>
-      <c r="H70" t="n">
+      <c r="H71" t="n">
         <v>16.5291461412151</v>
       </c>
-      <c r="I70" t="n">
+      <c r="I71" t="n">
         <v>11.37550200803213</v>
       </c>
-      <c r="J70" t="n">
+      <c r="J71" t="n">
         <v>11.93247126436782</v>
       </c>
-      <c r="K70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="K71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>Qwen3-VL-235B-A22B-Think-sub</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>temperature: 1.0
 top_k: 20
@@ -3277,39 +3369,39 @@
 presence_penalty: 0.0</t>
         </is>
       </c>
-      <c r="C71" t="n">
-        <v>64</v>
-      </c>
-      <c r="D71" t="n">
+      <c r="C72" t="n">
+        <v>64</v>
+      </c>
+      <c r="D72" t="n">
         <v>26.3</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E72" t="n">
         <v>26.98398576512455</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F72" t="n">
         <v>25.9995183044316</v>
       </c>
-      <c r="G71" t="n">
+      <c r="G72" t="n">
         <v>44.9</v>
       </c>
-      <c r="H71" t="n">
+      <c r="H72" t="n">
         <v>31.96223316912972</v>
       </c>
-      <c r="I71" t="n">
+      <c r="I72" t="n">
         <v>27.48159303882196</v>
       </c>
-      <c r="J71" t="n">
+      <c r="J72" t="n">
         <v>22.25574712643678</v>
       </c>
-      <c r="K71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="K72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>Qwen3-VL-235B-A22B-Think-sub</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>temperature: 1.0
 top_k: 20
@@ -3319,39 +3411,39 @@
 presence_penalty: 0.0</t>
         </is>
       </c>
-      <c r="C72" t="n">
+      <c r="C73" t="n">
         <v>512</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D73" t="n">
         <v>28.1</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E73" t="n">
         <v>27.76690391459075</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F73" t="n">
         <v>28.27552986512524</v>
       </c>
-      <c r="G72" t="n">
+      <c r="G73" t="n">
         <v>47.2</v>
       </c>
-      <c r="H72" t="n">
+      <c r="H73" t="n">
         <v>32.59646962233169</v>
       </c>
-      <c r="I72" t="n">
+      <c r="I73" t="n">
         <v>30.32295850066934</v>
       </c>
-      <c r="J72" t="n">
+      <c r="J73" t="n">
         <v>23.87931034482759</v>
       </c>
-      <c r="K72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="K73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>Qwen3-VL-235B-A22B-Think-sub-interleave</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>temperature: 1.0
 top_k: 20
@@ -3361,115 +3453,115 @@
 presence_penalty: 0.0</t>
         </is>
       </c>
-      <c r="C73" t="n">
+      <c r="C74" t="n">
         <v>512</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D74" t="n">
         <v>30.3</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E74" t="n">
         <v>28.72924080664294</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F74" t="n">
         <v>31.10549132947977</v>
       </c>
-      <c r="G73" t="n">
+      <c r="G74" t="n">
         <v>49</v>
       </c>
-      <c r="H73" t="n">
+      <c r="H74" t="n">
         <v>43.81773399014779</v>
       </c>
-      <c r="I73" t="n">
+      <c r="I74" t="n">
         <v>28.64625167336011</v>
       </c>
-      <c r="J73" t="n">
+      <c r="J74" t="n">
         <v>23.5308908045977</v>
       </c>
-      <c r="K73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="K74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>KimiVL-16B-A3B-Think</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>temperature: 0.8
 max_tokens: 32768</t>
         </is>
       </c>
-      <c r="C74" t="n">
-        <v>64</v>
-      </c>
-      <c r="D74" t="n">
+      <c r="C75" t="n">
+        <v>64</v>
+      </c>
+      <c r="D75" t="n">
         <v>11.7</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E75" t="n">
         <v>9.918446026097271</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F75" t="n">
         <v>12.65655105973025</v>
       </c>
-      <c r="G74" t="n">
+      <c r="G75" t="n">
         <v>27.3</v>
       </c>
-      <c r="H74" t="n">
+      <c r="H75" t="n">
         <v>16.38752052545156</v>
       </c>
-      <c r="I74" t="n">
+      <c r="I75" t="n">
         <v>10.61077643908969</v>
       </c>
-      <c r="J74" t="n">
+      <c r="J75" t="n">
         <v>9.732998084291188</v>
       </c>
-      <c r="K74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="K75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>KimiVL-16B-A3B-Think-sub</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>temperature: 0.8
 max_tokens: 32768</t>
         </is>
       </c>
-      <c r="C75" t="n">
-        <v>64</v>
-      </c>
-      <c r="D75" t="n">
+      <c r="C76" t="n">
+        <v>64</v>
+      </c>
+      <c r="D76" t="n">
         <v>15.7</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E76" t="n">
         <v>17.11298932384341</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F76" t="n">
         <v>14.88439306358381</v>
       </c>
-      <c r="G75" t="n">
+      <c r="G76" t="n">
         <v>32.4</v>
       </c>
-      <c r="H75" t="n">
+      <c r="H76" t="n">
         <v>21.82266009852217</v>
       </c>
-      <c r="I75" t="n">
+      <c r="I76" t="n">
         <v>14.01104417670683</v>
       </c>
-      <c r="J75" t="n">
+      <c r="J76" t="n">
         <v>13.26149425287356</v>
       </c>
-      <c r="K75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="K76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>MiMo-VL-7B-RL-2508</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>n_frame: 64
 temperature: 0.3
@@ -3478,39 +3570,39 @@
 max_tokens: 16384</t>
         </is>
       </c>
-      <c r="C76" t="n">
-        <v>64</v>
-      </c>
-      <c r="D76" t="n">
+      <c r="C77" t="n">
+        <v>64</v>
+      </c>
+      <c r="D77" t="n">
         <v>11.9</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E77" t="n">
         <v>10.76957295373665</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F77" t="n">
         <v>12.45183044315992</v>
       </c>
-      <c r="G76" t="n">
+      <c r="G77" t="n">
         <v>27</v>
       </c>
-      <c r="H76" t="n">
+      <c r="H77" t="n">
         <v>16.0940065681445</v>
       </c>
-      <c r="I76" t="n">
+      <c r="I77" t="n">
         <v>12.47322623828648</v>
       </c>
-      <c r="J76" t="n">
+      <c r="J77" t="n">
         <v>8.953544061302683</v>
       </c>
-      <c r="K76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="K77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>MiMo-VL-7B-RL-2508-sub</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>n_frame: 64
 temperature: 0.3
@@ -3519,39 +3611,39 @@
 max_tokens: 16384</t>
         </is>
       </c>
-      <c r="C77" t="n">
-        <v>64</v>
-      </c>
-      <c r="D77" t="n">
+      <c r="C78" t="n">
+        <v>64</v>
+      </c>
+      <c r="D78" t="n">
         <v>19.4</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E78" t="n">
         <v>20.32325029655991</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F78" t="n">
         <v>18.90655105973025</v>
       </c>
-      <c r="G77" t="n">
+      <c r="G78" t="n">
         <v>36</v>
       </c>
-      <c r="H77" t="n">
+      <c r="H78" t="n">
         <v>24.92816091954023</v>
       </c>
-      <c r="I77" t="n">
+      <c r="I78" t="n">
         <v>18.76506024096386</v>
       </c>
-      <c r="J77" t="n">
+      <c r="J78" t="n">
         <v>16.63912835249042</v>
       </c>
-      <c r="K77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="K78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>GLM4.1v-think</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>max_tokens: 16384
 temperature: 0.8
@@ -3560,39 +3652,39 @@
 num_frames: 64</t>
         </is>
       </c>
-      <c r="C78" t="n">
-        <v>64</v>
-      </c>
-      <c r="D78" t="n">
+      <c r="C79" t="n">
+        <v>64</v>
+      </c>
+      <c r="D79" t="n">
         <v>9.4</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E79" t="n">
         <v>7.252372479240807</v>
       </c>
-      <c r="F78" t="n">
+      <c r="F79" t="n">
         <v>10.621387283237</v>
       </c>
-      <c r="G78" t="n">
+      <c r="G79" t="n">
         <v>23.7</v>
       </c>
-      <c r="H78" t="n">
+      <c r="H79" t="n">
         <v>14.07224958949097</v>
       </c>
-      <c r="I78" t="n">
+      <c r="I79" t="n">
         <v>7.505020080321285</v>
       </c>
-      <c r="J78" t="n">
+      <c r="J79" t="n">
         <v>8.117816091954023</v>
       </c>
-      <c r="K78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="K79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>GLM4.1v-think-sub</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>max_tokens: 16384
 temperature: 0.8
@@ -3601,39 +3693,39 @@
 num_frames: 64</t>
         </is>
       </c>
-      <c r="C79" t="n">
-        <v>64</v>
-      </c>
-      <c r="D79" t="n">
+      <c r="C80" t="n">
+        <v>64</v>
+      </c>
+      <c r="D80" t="n">
         <v>14</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E80" t="n">
         <v>14.40094899169632</v>
       </c>
-      <c r="F79" t="n">
+      <c r="F80" t="n">
         <v>13.76445086705202</v>
       </c>
-      <c r="G79" t="n">
+      <c r="G80" t="n">
         <v>30.3</v>
       </c>
-      <c r="H79" t="n">
+      <c r="H80" t="n">
         <v>18.78899835796387</v>
       </c>
-      <c r="I79" t="n">
+      <c r="I80" t="n">
         <v>13.17269076305221</v>
       </c>
-      <c r="J79" t="n">
+      <c r="J80" t="n">
         <v>11.77083333333333</v>
       </c>
-      <c r="K79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="K80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>GLM4.5v-think</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>max_tokens: 16384
 temperature: 1.0
@@ -3642,39 +3734,39 @@
 num_frames: 64</t>
         </is>
       </c>
-      <c r="C80" t="n">
-        <v>64</v>
-      </c>
-      <c r="D80" t="n">
+      <c r="C81" t="n">
+        <v>64</v>
+      </c>
+      <c r="D81" t="n">
         <v>13.3</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E81" t="n">
         <v>10.63315539739027</v>
       </c>
-      <c r="F80" t="n">
+      <c r="F81" t="n">
         <v>14.72784200385357</v>
       </c>
-      <c r="G80" t="n">
+      <c r="G81" t="n">
         <v>29.6</v>
       </c>
-      <c r="H80" t="n">
+      <c r="H81" t="n">
         <v>14.86247947454844</v>
       </c>
-      <c r="I80" t="n">
+      <c r="I81" t="n">
         <v>14.67034805890228</v>
       </c>
-      <c r="J80" t="n">
+      <c r="J81" t="n">
         <v>11.38409961685824</v>
       </c>
-      <c r="K80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="K81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>GLM4.5v-think-sub</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>max_tokens: 16384
 temperature: 1.0
@@ -3683,39 +3775,39 @@
 num_frames: 64</t>
         </is>
       </c>
-      <c r="C81" t="n">
-        <v>64</v>
-      </c>
-      <c r="D81" t="n">
+      <c r="C82" t="n">
+        <v>64</v>
+      </c>
+      <c r="D82" t="n">
         <v>21.8</v>
       </c>
-      <c r="E81" t="n">
+      <c r="E82" t="n">
         <v>24.28825622775801</v>
       </c>
-      <c r="F81" t="n">
+      <c r="F82" t="n">
         <v>20.52023121387283</v>
       </c>
-      <c r="G81" t="n">
+      <c r="G82" t="n">
         <v>39.2</v>
       </c>
-      <c r="H81" t="n">
+      <c r="H82" t="n">
         <v>26.17610837438423</v>
       </c>
-      <c r="I81" t="n">
+      <c r="I82" t="n">
         <v>21.74531459170013</v>
       </c>
-      <c r="J81" t="n">
+      <c r="J82" t="n">
         <v>19.38697318007663</v>
       </c>
-      <c r="K81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="K82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>GLM4.6-flash</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>temperature: 0.8
 repetition_penalty: 1.1
@@ -3724,39 +3816,39 @@
 num_frames: 64</t>
         </is>
       </c>
-      <c r="C82" t="n">
-        <v>64</v>
-      </c>
-      <c r="D82" t="n">
+      <c r="C83" t="n">
+        <v>64</v>
+      </c>
+      <c r="D83" t="n">
         <v>12.7</v>
       </c>
-      <c r="E82" t="n">
+      <c r="E83" t="n">
         <v>10.30249110320285</v>
       </c>
-      <c r="F82" t="n">
+      <c r="F83" t="n">
         <v>13.98121387283237</v>
       </c>
-      <c r="G82" t="n">
+      <c r="G83" t="n">
         <v>27.7</v>
       </c>
-      <c r="H82" t="n">
+      <c r="H83" t="n">
         <v>17.33990147783251</v>
       </c>
-      <c r="I82" t="n">
+      <c r="I83" t="n">
         <v>13.39022757697456</v>
       </c>
-      <c r="J82" t="n">
+      <c r="J83" t="n">
         <v>9.474377394636015</v>
       </c>
-      <c r="K82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="K83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>GLM4.6-flash-sub</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>temperature: 0.8
 repetition_penalty: 1.1
@@ -3765,39 +3857,39 @@
 num_frames: 64</t>
         </is>
       </c>
-      <c r="C83" t="n">
-        <v>64</v>
-      </c>
-      <c r="D83" t="n">
+      <c r="C84" t="n">
+        <v>64</v>
+      </c>
+      <c r="D84" t="n">
         <v>19.8</v>
       </c>
-      <c r="E83" t="n">
+      <c r="E84" t="n">
         <v>19.96144721233689</v>
       </c>
-      <c r="F83" t="n">
+      <c r="F84" t="n">
         <v>19.64113680154142</v>
       </c>
-      <c r="G83" t="n">
+      <c r="G84" t="n">
         <v>37.4</v>
       </c>
-      <c r="H83" t="n">
+      <c r="H84" t="n">
         <v>26.78571428571428</v>
       </c>
-      <c r="I83" t="n">
+      <c r="I84" t="n">
         <v>19.38755020080321</v>
       </c>
-      <c r="J83" t="n">
+      <c r="J84" t="n">
         <v>15.91355363984674</v>
       </c>
-      <c r="K83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="K84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>Qwen3.5-4B</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>temperature=1.0,
 top_p=0.95,
@@ -3806,39 +3898,39 @@
 max_new_tokens=32768,</t>
         </is>
       </c>
-      <c r="C84" t="n">
-        <v>64</v>
-      </c>
-      <c r="D84" t="n">
+      <c r="C85" t="n">
+        <v>64</v>
+      </c>
+      <c r="D85" t="n">
         <v>11.6</v>
       </c>
-      <c r="E84" t="n">
+      <c r="E85" t="n">
         <v>10.02965599051008</v>
       </c>
-      <c r="F84" t="n">
+      <c r="F85" t="n">
         <v>12.37957610789981</v>
       </c>
-      <c r="G84" t="n">
+      <c r="G85" t="n">
         <v>26.5</v>
       </c>
-      <c r="H84" t="n">
+      <c r="H85" t="n">
         <v>14.90353037766831</v>
       </c>
-      <c r="I84" t="n">
+      <c r="I85" t="n">
         <v>11.10107095046854</v>
       </c>
-      <c r="J84" t="n">
+      <c r="J85" t="n">
         <v>9.924568965517242</v>
       </c>
-      <c r="K84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="K85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>Qwen3.5-4B-sub</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>temperature=1.0,
 top_p=0.95,
@@ -3847,39 +3939,39 @@
 max_new_tokens=32768,</t>
         </is>
       </c>
-      <c r="C85" t="n">
-        <v>64</v>
-      </c>
-      <c r="D85" t="n">
+      <c r="C86" t="n">
+        <v>64</v>
+      </c>
+      <c r="D86" t="n">
         <v>20.7</v>
       </c>
-      <c r="E85" t="n">
+      <c r="E86" t="n">
         <v>21.39679715302491</v>
       </c>
-      <c r="F85" t="n">
+      <c r="F86" t="n">
         <v>20.35163776493256</v>
       </c>
-      <c r="G85" t="n">
+      <c r="G86" t="n">
         <v>38.8</v>
       </c>
-      <c r="H85" t="n">
+      <c r="H86" t="n">
         <v>26.23357963875205</v>
       </c>
-      <c r="I85" t="n">
+      <c r="I86" t="n">
         <v>21.02409638554217</v>
       </c>
-      <c r="J85" t="n">
+      <c r="J86" t="n">
         <v>17.28328544061302</v>
       </c>
-      <c r="K85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="K86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>Qwen3.5-9B</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>temperature=1.0,
 top_p=0.95,
@@ -3888,39 +3980,39 @@
 max_new_tokens=32768,</t>
         </is>
       </c>
-      <c r="C86" t="n">
-        <v>64</v>
-      </c>
-      <c r="D86" t="n">
+      <c r="C87" t="n">
+        <v>64</v>
+      </c>
+      <c r="D87" t="n">
         <v>13.7</v>
       </c>
-      <c r="E86" t="n">
+      <c r="E87" t="n">
         <v>13.12425860023725</v>
       </c>
-      <c r="F86" t="n">
+      <c r="F87" t="n">
         <v>13.94508670520231</v>
       </c>
-      <c r="G86" t="n">
+      <c r="G87" t="n">
         <v>28.9</v>
       </c>
-      <c r="H86" t="n">
+      <c r="H87" t="n">
         <v>16.69745484400657</v>
       </c>
-      <c r="I86" t="n">
+      <c r="I87" t="n">
         <v>12.63052208835341</v>
       </c>
-      <c r="J86" t="n">
+      <c r="J87" t="n">
         <v>12.61733716475096</v>
       </c>
-      <c r="K86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="K87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>Qwen3.5-9B</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>temperature=1.0,
 top_p=0.95,
@@ -3929,39 +4021,39 @@
 max_new_tokens=32768,</t>
         </is>
       </c>
-      <c r="C87" t="n">
+      <c r="C88" t="n">
         <v>512</v>
       </c>
-      <c r="D87" t="n">
+      <c r="D88" t="n">
         <v>19.5</v>
       </c>
-      <c r="E87" t="n">
+      <c r="E88" t="n">
         <v>16.84311981020166</v>
       </c>
-      <c r="F87" t="n">
+      <c r="F88" t="n">
         <v>20.98988439306358</v>
       </c>
-      <c r="G87" t="n">
+      <c r="G88" t="n">
         <v>36.8</v>
       </c>
-      <c r="H87" t="n">
+      <c r="H88" t="n">
         <v>21.83908045977011</v>
       </c>
-      <c r="I87" t="n">
+      <c r="I88" t="n">
         <v>24.48962516733601</v>
       </c>
-      <c r="J87" t="n">
+      <c r="J88" t="n">
         <v>14.64200191570881</v>
       </c>
-      <c r="K87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="K88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>Qwen3.5-9B-sub</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>temperature=1.0,
 top_p=0.95,
@@ -3970,39 +4062,39 @@
 max_new_tokens=32768,</t>
         </is>
       </c>
-      <c r="C88" t="n">
-        <v>64</v>
-      </c>
-      <c r="D88" t="n">
+      <c r="C89" t="n">
+        <v>64</v>
+      </c>
+      <c r="D89" t="n">
         <v>23.2</v>
       </c>
-      <c r="E88" t="n">
+      <c r="E89" t="n">
         <v>22.24792408066429</v>
       </c>
-      <c r="F88" t="n">
+      <c r="F89" t="n">
         <v>23.63921001926782</v>
       </c>
-      <c r="G88" t="n">
+      <c r="G89" t="n">
         <v>40.3</v>
       </c>
-      <c r="H88" t="n">
+      <c r="H89" t="n">
         <v>28.26354679802956</v>
       </c>
-      <c r="I88" t="n">
+      <c r="I89" t="n">
         <v>24.73226238286479</v>
       </c>
-      <c r="J88" t="n">
+      <c r="J89" t="n">
         <v>19.03615900383142</v>
       </c>
-      <c r="K88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="K89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>Qwen3.5-9B-sub</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>temperature=1.0,
 top_p=0.95,
@@ -4011,39 +4103,39 @@
 max_new_tokens=32768,</t>
         </is>
       </c>
-      <c r="C89" t="n">
+      <c r="C90" t="n">
         <v>512</v>
       </c>
-      <c r="D89" t="n">
+      <c r="D90" t="n">
         <v>26.2</v>
       </c>
-      <c r="E89" t="n">
+      <c r="E90" t="n">
         <v>26.80308422301305</v>
       </c>
-      <c r="F89" t="n">
+      <c r="F90" t="n">
         <v>25.84296724470135</v>
       </c>
-      <c r="G89" t="n">
+      <c r="G90" t="n">
         <v>44.5</v>
       </c>
-      <c r="H89" t="n">
+      <c r="H90" t="n">
         <v>30.47413793103448</v>
       </c>
-      <c r="I89" t="n">
+      <c r="I90" t="n">
         <v>30.11880856760375</v>
       </c>
-      <c r="J89" t="n">
+      <c r="J90" t="n">
         <v>20.85727969348659</v>
       </c>
-      <c r="K89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="K90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>Qwen3.5-27B</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>temperature=1.0,
 top_p=0.95,
@@ -4052,39 +4144,39 @@
 max_new_tokens=32768,</t>
         </is>
       </c>
-      <c r="C90" t="n">
-        <v>64</v>
-      </c>
-      <c r="D90" t="n">
+      <c r="C91" t="n">
+        <v>64</v>
+      </c>
+      <c r="D91" t="n">
         <v>17.6</v>
       </c>
-      <c r="E90" t="n">
+      <c r="E91" t="n">
         <v>16.42497034400949</v>
       </c>
-      <c r="F90" t="n">
+      <c r="F91" t="n">
         <v>18.18400770712909</v>
       </c>
-      <c r="G90" t="n">
+      <c r="G91" t="n">
         <v>34.5</v>
       </c>
-      <c r="H90" t="n">
+      <c r="H91" t="n">
         <v>19.98152709359606</v>
       </c>
-      <c r="I90" t="n">
+      <c r="I91" t="n">
         <v>18.50568942436412</v>
       </c>
-      <c r="J90" t="n">
+      <c r="J91" t="n">
         <v>15.48491379310345</v>
       </c>
-      <c r="K90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="K91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>Qwen3.5-27B</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>temperature=1.0,
 top_p=0.95,
@@ -4093,39 +4185,39 @@
 max_new_tokens=32768,</t>
         </is>
       </c>
-      <c r="C91" t="n">
+      <c r="C92" t="n">
         <v>512</v>
       </c>
-      <c r="D91" t="n">
+      <c r="D92" t="n">
         <v>19.5</v>
       </c>
-      <c r="E91" t="n">
+      <c r="E92" t="n">
         <v>16.47390272835113</v>
       </c>
-      <c r="F91" t="n">
+      <c r="F92" t="n">
         <v>20.59248554913295</v>
       </c>
-      <c r="G91" t="n">
+      <c r="G92" t="n">
         <v>37.4</v>
       </c>
-      <c r="H91" t="n">
+      <c r="H92" t="n">
         <v>22.31732348111658</v>
       </c>
-      <c r="I91" t="n">
+      <c r="I92" t="n">
         <v>23.14926372155288</v>
       </c>
-      <c r="J91" t="n">
+      <c r="J92" t="n">
         <v>14.43127394636015</v>
       </c>
-      <c r="K91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="K92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>Qwen3.5-27B-sub</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>temperature=1.0,
 top_p=0.95,
@@ -4134,39 +4226,39 @@
 max_new_tokens=32768,</t>
         </is>
       </c>
-      <c r="C92" t="n">
-        <v>64</v>
-      </c>
-      <c r="D92" t="n">
+      <c r="C93" t="n">
+        <v>64</v>
+      </c>
+      <c r="D93" t="n">
         <v>29.6</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E93" t="n">
         <v>31.67111506524318</v>
       </c>
-      <c r="F92" t="n">
+      <c r="F93" t="n">
         <v>28.54046242774567</v>
       </c>
-      <c r="G92" t="n">
+      <c r="G93" t="n">
         <v>47.6</v>
       </c>
-      <c r="H92" t="n">
+      <c r="H93" t="n">
         <v>34.997947454844</v>
       </c>
-      <c r="I92" t="n">
+      <c r="I93" t="n">
         <v>30.58567603748326</v>
       </c>
-      <c r="J92" t="n">
+      <c r="J93" t="n">
         <v>25.83812260536398</v>
       </c>
-      <c r="K92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="K93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>Qwen3.5-27B-sub</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>temperature=1.0,
 top_p=0.95,
@@ -4175,39 +4267,39 @@
 max_new_tokens=32768,</t>
         </is>
       </c>
-      <c r="C93" t="n">
+      <c r="C94" t="n">
         <v>512</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D94" t="n">
         <v>31.4</v>
       </c>
-      <c r="E93" t="n">
+      <c r="E94" t="n">
         <v>31.25741399762752</v>
       </c>
-      <c r="F93" t="n">
+      <c r="F94" t="n">
         <v>31.51493256262042</v>
       </c>
-      <c r="G93" t="n">
+      <c r="G94" t="n">
         <v>49.6</v>
       </c>
-      <c r="H93" t="n">
+      <c r="H94" t="n">
         <v>34.35344827586207</v>
       </c>
-      <c r="I93" t="n">
+      <c r="I94" t="n">
         <v>36.39223560910307</v>
       </c>
-      <c r="J93" t="n">
+      <c r="J94" t="n">
         <v>26.16139846743295</v>
       </c>
-      <c r="K93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="K94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>Qwen3.5-A3B</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>temperature=1.0,
 top_p=0.95,
@@ -4216,39 +4308,39 @@
 max_new_tokens=32768,</t>
         </is>
       </c>
-      <c r="C94" t="n">
-        <v>64</v>
-      </c>
-      <c r="D94" t="n">
+      <c r="C95" t="n">
+        <v>64</v>
+      </c>
+      <c r="D95" t="n">
         <v>15.6</v>
       </c>
-      <c r="E94" t="n">
+      <c r="E95" t="n">
         <v>14.62930011862396</v>
       </c>
-      <c r="F94" t="n">
+      <c r="F95" t="n">
         <v>16.07658959537572</v>
       </c>
-      <c r="G94" t="n">
+      <c r="G95" t="n">
         <v>32.6</v>
       </c>
-      <c r="H94" t="n">
+      <c r="H95" t="n">
         <v>18.15476190476191</v>
       </c>
-      <c r="I94" t="n">
+      <c r="I95" t="n">
         <v>15.84672021419009</v>
       </c>
-      <c r="J94" t="n">
+      <c r="J95" t="n">
         <v>13.86015325670498</v>
       </c>
-      <c r="K94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="K95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>Qwen3.5-A3B</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>temperature=1.0,
 top_p=0.95,
@@ -4257,39 +4349,39 @@
 max_new_tokens=32768,</t>
         </is>
       </c>
-      <c r="C95" t="n">
+      <c r="C96" t="n">
         <v>512</v>
       </c>
-      <c r="D95" t="n">
+      <c r="D96" t="n">
         <v>12.2</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E96" t="n">
         <v>11.05130486358244</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F96" t="n">
         <v>12.78901734104046</v>
       </c>
-      <c r="G95" t="n">
+      <c r="G96" t="n">
         <v>28.5</v>
       </c>
-      <c r="H95" t="n">
+      <c r="H96" t="n">
         <v>13.93267651888342</v>
       </c>
-      <c r="I95" t="n">
+      <c r="I96" t="n">
         <v>11.39223560910308</v>
       </c>
-      <c r="J95" t="n">
+      <c r="J96" t="n">
         <v>11.71815134099617</v>
       </c>
-      <c r="K95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="K96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>Qwen3.5-A3B-sub</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>temperature=1.0,
 top_p=0.95,
@@ -4298,39 +4390,39 @@
 max_new_tokens=32768,</t>
         </is>
       </c>
-      <c r="C96" t="n">
-        <v>64</v>
-      </c>
-      <c r="D96" t="n">
+      <c r="C97" t="n">
+        <v>64</v>
+      </c>
+      <c r="D97" t="n">
         <v>25.8</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>27.53855278766311</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>24.85549132947977</v>
       </c>
-      <c r="G96" t="n">
+      <c r="G97" t="n">
         <v>43.9</v>
       </c>
-      <c r="H96" t="n">
+      <c r="H97" t="n">
         <v>31.2828407224959</v>
       </c>
-      <c r="I96" t="n">
+      <c r="I97" t="n">
         <v>24.89457831325301</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>23.24473180076629</v>
       </c>
-      <c r="K96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="K97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
         <is>
           <t>Qwen3.5-A3B-sub</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>temperature=1.0,
 top_p=0.95,
@@ -4339,39 +4431,39 @@
 max_new_tokens=32768,</t>
         </is>
       </c>
-      <c r="C97" t="n">
+      <c r="C98" t="n">
         <v>512</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D98" t="n">
         <v>23.9</v>
       </c>
-      <c r="E97" t="n">
+      <c r="E98" t="n">
         <v>24.69750889679715</v>
       </c>
-      <c r="F97" t="n">
+      <c r="F98" t="n">
         <v>23.39836223506744</v>
       </c>
-      <c r="G97" t="n">
+      <c r="G98" t="n">
         <v>41.5</v>
       </c>
-      <c r="H97" t="n">
+      <c r="H98" t="n">
         <v>29.54022988505747</v>
       </c>
-      <c r="I97" t="n">
+      <c r="I98" t="n">
         <v>24.49966532797858</v>
       </c>
-      <c r="J97" t="n">
+      <c r="J98" t="n">
         <v>20.07662835249042</v>
       </c>
-      <c r="K97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="K98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>Qwen3.5-A10B</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>temperature=1.0,
 top_p=0.95,
@@ -4380,39 +4472,39 @@
 max_new_tokens=32768,</t>
         </is>
       </c>
-      <c r="C98" t="n">
-        <v>64</v>
-      </c>
-      <c r="D98" t="n">
+      <c r="C99" t="n">
+        <v>64</v>
+      </c>
+      <c r="D99" t="n">
         <v>16.3</v>
       </c>
-      <c r="E98" t="n">
+      <c r="E99" t="n">
         <v>15.26986951364175</v>
       </c>
-      <c r="F98" t="n">
+      <c r="F99" t="n">
         <v>16.79913294797688</v>
       </c>
-      <c r="G98" t="n">
+      <c r="G99" t="n">
         <v>33</v>
       </c>
-      <c r="H98" t="n">
+      <c r="H99" t="n">
         <v>18.95730706075534</v>
       </c>
-      <c r="I98" t="n">
+      <c r="I99" t="n">
         <v>15.99062918340027</v>
       </c>
-      <c r="J98" t="n">
+      <c r="J99" t="n">
         <v>14.8838601532567</v>
       </c>
-      <c r="K98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="K99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>Qwen3.5-A10B</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>temperature=1.0,
 top_p=0.95,
@@ -4421,39 +4513,39 @@
 max_new_tokens=32768,</t>
         </is>
       </c>
-      <c r="C99" t="n">
+      <c r="C100" t="n">
         <v>512</v>
       </c>
-      <c r="D99" t="n">
+      <c r="D100" t="n">
         <v>14</v>
       </c>
-      <c r="E99" t="n">
+      <c r="E100" t="n">
         <v>12.89590747330961</v>
       </c>
-      <c r="F99" t="n">
+      <c r="F100" t="n">
         <v>14.54720616570328</v>
       </c>
-      <c r="G99" t="n">
+      <c r="G100" t="n">
         <v>30.6</v>
       </c>
-      <c r="H99" t="n">
+      <c r="H100" t="n">
         <v>15.77175697865353</v>
       </c>
-      <c r="I99" t="n">
+      <c r="I100" t="n">
         <v>13.95749665327978</v>
       </c>
-      <c r="J99" t="n">
+      <c r="J100" t="n">
         <v>12.92145593869732</v>
       </c>
-      <c r="K99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="K100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>Qwen3.5-A10B-sub</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>temperature=1.0,
 top_p=0.95,
@@ -4462,39 +4554,39 @@
 max_new_tokens=32768,</t>
         </is>
       </c>
-      <c r="C100" t="n">
-        <v>64</v>
-      </c>
-      <c r="D100" t="n">
+      <c r="C101" t="n">
+        <v>64</v>
+      </c>
+      <c r="D101" t="n">
         <v>26.7</v>
       </c>
-      <c r="E100" t="n">
+      <c r="E101" t="n">
         <v>27.25533807829181</v>
       </c>
-      <c r="F100" t="n">
+      <c r="F101" t="n">
         <v>26.42100192678227</v>
       </c>
-      <c r="G100" t="n">
+      <c r="G101" t="n">
         <v>45.1</v>
       </c>
-      <c r="H100" t="n">
+      <c r="H101" t="n">
         <v>30.11288998357964</v>
       </c>
-      <c r="I100" t="n">
+      <c r="I101" t="n">
         <v>27.88152610441767</v>
       </c>
-      <c r="J100" t="n">
+      <c r="J101" t="n">
         <v>23.89607279693487</v>
       </c>
-      <c r="K100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="K101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>Qwen3.5-A10B-sub</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>temperature=1.0,
 top_p=0.95,
@@ -4503,39 +4595,39 @@
 max_new_tokens=32768,</t>
         </is>
       </c>
-      <c r="C101" t="n">
+      <c r="C102" t="n">
         <v>512</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D102" t="n">
         <v>25.1</v>
       </c>
-      <c r="E101" t="n">
+      <c r="E102" t="n">
         <v>26.47983392645314</v>
       </c>
-      <c r="F101" t="n">
+      <c r="F102" t="n">
         <v>24.33766859344894</v>
       </c>
-      <c r="G101" t="n">
+      <c r="G102" t="n">
         <v>43.4</v>
       </c>
-      <c r="H101" t="n">
+      <c r="H102" t="n">
         <v>27.44663382594417</v>
       </c>
-      <c r="I101" t="n">
+      <c r="I102" t="n">
         <v>25.56392235609103</v>
       </c>
-      <c r="J101" t="n">
+      <c r="J102" t="n">
         <v>23.3764367816092</v>
       </c>
-      <c r="K101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="K102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>Qwen3.5-A17B</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>temperature=1.0,
 top_p=0.95,
@@ -4544,39 +4636,39 @@
 max_new_tokens=32768,</t>
         </is>
       </c>
-      <c r="C102" t="n">
-        <v>64</v>
-      </c>
-      <c r="D102" t="n">
+      <c r="C103" t="n">
+        <v>64</v>
+      </c>
+      <c r="D103" t="n">
         <v>20.7</v>
       </c>
-      <c r="E102" t="n">
+      <c r="E103" t="n">
         <v>20.3929418742586</v>
       </c>
-      <c r="F102" t="n">
+      <c r="F103" t="n">
         <v>20.86946050096339</v>
       </c>
-      <c r="G102" t="n">
+      <c r="G103" t="n">
         <v>39.3</v>
       </c>
-      <c r="H102" t="n">
+      <c r="H103" t="n">
         <v>20.71018062397373</v>
       </c>
-      <c r="I102" t="n">
+      <c r="I103" t="n">
         <v>23.10073627844712</v>
       </c>
-      <c r="J102" t="n">
+      <c r="J103" t="n">
         <v>18.98108237547893</v>
       </c>
-      <c r="K102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="K103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>Qwen3.5-A17B</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>temperature=1.0,
 top_p=0.95,
@@ -4585,39 +4677,39 @@
 max_new_tokens=32768,</t>
         </is>
       </c>
-      <c r="C103" t="n">
+      <c r="C104" t="n">
         <v>512</v>
       </c>
-      <c r="D103" t="n">
+      <c r="D104" t="n">
         <v>30.3</v>
       </c>
-      <c r="E103" t="n">
+      <c r="E104" t="n">
         <v>26.90984578884935</v>
       </c>
-      <c r="F103" t="n">
+      <c r="F104" t="n">
         <v>32.17726396917148</v>
       </c>
-      <c r="G103" t="n">
+      <c r="G104" t="n">
         <v>48.8</v>
       </c>
-      <c r="H103" t="n">
+      <c r="H104" t="n">
         <v>35.43308702791462</v>
       </c>
-      <c r="I103" t="n">
+      <c r="I104" t="n">
         <v>36.50267737617135</v>
       </c>
-      <c r="J103" t="n">
+      <c r="J104" t="n">
         <v>22.92983716475096</v>
       </c>
-      <c r="K103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="K104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
         <is>
           <t>Qwen3.5-A17B-sub</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>temperature=1.0,
 top_p=0.95,
@@ -4626,39 +4718,39 @@
 max_new_tokens=32768,</t>
         </is>
       </c>
-      <c r="C104" t="n">
-        <v>64</v>
-      </c>
-      <c r="D104" t="n">
+      <c r="C105" t="n">
+        <v>64</v>
+      </c>
+      <c r="D105" t="n">
         <v>30.6</v>
       </c>
-      <c r="E104" t="n">
+      <c r="E105" t="n">
         <v>32.69276393831554</v>
       </c>
-      <c r="F104" t="n">
+      <c r="F105" t="n">
         <v>29.50385356454721</v>
       </c>
-      <c r="G104" t="n">
+      <c r="G105" t="n">
         <v>48.9</v>
       </c>
-      <c r="H104" t="n">
+      <c r="H105" t="n">
         <v>34.79064039408867</v>
       </c>
-      <c r="I104" t="n">
+      <c r="I105" t="n">
         <v>30.36479250334672</v>
       </c>
-      <c r="J104" t="n">
+      <c r="J105" t="n">
         <v>28.37883141762452</v>
       </c>
-      <c r="K104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="K105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
         <is>
           <t>Qwen3.5-A17B-sub</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>temperature=1.0,
 top_p=0.95,
@@ -4667,69 +4759,36 @@
 max_new_tokens=32768,</t>
         </is>
       </c>
-      <c r="C105" t="n">
+      <c r="C106" t="n">
         <v>512</v>
       </c>
-      <c r="D105" t="n">
+      <c r="D106" t="n">
         <v>39.1</v>
       </c>
-      <c r="E105" t="n">
+      <c r="E106" t="n">
         <v>39.36091340450771</v>
       </c>
-      <c r="F105" t="n">
+      <c r="F106" t="n">
         <v>38.95712909441233</v>
       </c>
-      <c r="G105" t="n">
+      <c r="G106" t="n">
         <v>55.9</v>
       </c>
-      <c r="H105" t="n">
+      <c r="H106" t="n">
         <v>50.30993431855501</v>
       </c>
-      <c r="I105" t="n">
+      <c r="I106" t="n">
         <v>41.7553547523427</v>
       </c>
-      <c r="J105" t="n">
+      <c r="J106" t="n">
         <v>30.65852490421456</v>
-      </c>
-      <c r="K105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Qwen3.5-Omni-Plus-wo_audio</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
-      <c r="C106" t="n">
-        <v>64</v>
-      </c>
-      <c r="D106" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="E106" t="n">
-        <v>17.22419928825623</v>
-      </c>
-      <c r="F106" t="n">
-        <v>17.31695568400771</v>
-      </c>
-      <c r="G106" t="n">
-        <v>35</v>
-      </c>
-      <c r="H106" t="n">
-        <v>19.62643678160919</v>
-      </c>
-      <c r="I106" t="n">
-        <v>18.21954484605087</v>
-      </c>
-      <c r="J106" t="n">
-        <v>15.24904214559387</v>
       </c>
       <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Qwen3.5-Omni-Plus-w_audio</t>
+          <t>Qwen3.5-Omni-Plus-wo_audio</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4737,27 +4796,126 @@
         <v>64</v>
       </c>
       <c r="D107" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="E107" t="n">
+        <v>17.22419928825623</v>
+      </c>
+      <c r="F107" t="n">
+        <v>17.31695568400771</v>
+      </c>
+      <c r="G107" t="n">
+        <v>35</v>
+      </c>
+      <c r="H107" t="n">
+        <v>19.62643678160919</v>
+      </c>
+      <c r="I107" t="n">
+        <v>18.21954484605087</v>
+      </c>
+      <c r="J107" t="n">
+        <v>15.24904214559387</v>
+      </c>
+      <c r="K107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Qwen3.5-Omni-Plus-w_audio</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="n">
+        <v>64</v>
+      </c>
+      <c r="D108" t="n">
         <v>25.6</v>
       </c>
-      <c r="E107" t="n">
+      <c r="E108" t="n">
         <v>25.98457888493476</v>
       </c>
-      <c r="F107" t="n">
+      <c r="F108" t="n">
         <v>25.34922928709056</v>
       </c>
-      <c r="G107" t="n">
+      <c r="G108" t="n">
         <v>44.3</v>
       </c>
-      <c r="H107" t="n">
+      <c r="H108" t="n">
         <v>31.17610837438423</v>
       </c>
-      <c r="I107" t="n">
+      <c r="I108" t="n">
         <v>26.61311914323963</v>
       </c>
-      <c r="J107" t="n">
+      <c r="J108" t="n">
         <v>21.55890804597701</v>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Qwen3.5-Omni-Plus-wo_audio</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="n">
+        <v>512</v>
+      </c>
+      <c r="D109" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="E109" t="n">
+        <v>15.27431791221827</v>
+      </c>
+      <c r="F109" t="n">
+        <v>21.45953757225433</v>
+      </c>
+      <c r="G109" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="H109" t="n">
+        <v>21.25410509031198</v>
+      </c>
+      <c r="I109" t="n">
+        <v>24.33065595716198</v>
+      </c>
+      <c r="J109" t="n">
+        <v>14.53065134099617</v>
+      </c>
+      <c r="K109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Qwen3.5-Omni-Plus-w_audio</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="n">
+        <v>512</v>
+      </c>
+      <c r="D110" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E110" t="n">
+        <v>26.97212336892052</v>
+      </c>
+      <c r="F110" t="n">
+        <v>27.58911368015414</v>
+      </c>
+      <c r="G110" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="H110" t="n">
+        <v>37.36247947454844</v>
+      </c>
+      <c r="I110" t="n">
+        <v>27.89825970548862</v>
+      </c>
+      <c r="J110" t="n">
+        <v>21.16858237547893</v>
+      </c>
+      <c r="K110" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
